--- a/data/20260622_台股財報估值.xlsx
+++ b/data/20260622_台股財報估值.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V133"/>
+  <dimension ref="A1:V135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1842,12 +1842,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>茂達</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -1857,69 +1857,69 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2.6</v>
+        <v>7.1</v>
       </c>
       <c r="F20" t="n">
-        <v>14.9</v>
+        <v>2.1</v>
       </c>
       <c r="G20" t="n">
         <v>24.2</v>
       </c>
       <c r="H20" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I20" t="n">
-        <v>18.3</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
-        <v>16.3</v>
+        <v>1.5</v>
       </c>
       <c r="K20" t="n">
-        <v>14.12</v>
+        <v>6.96</v>
       </c>
       <c r="L20" t="n">
-        <v>28.8</v>
+        <v>17.5</v>
       </c>
       <c r="M20" t="n">
-        <v>39.7</v>
+        <v>88.2</v>
       </c>
       <c r="N20" t="n">
-        <v>215</v>
+        <v>45</v>
       </c>
       <c r="O20" t="n">
-        <v>1.21</v>
+        <v>6.49</v>
       </c>
       <c r="P20" t="n">
-        <v>13.2</v>
+        <v>62.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>394</v>
+        <v>188</v>
       </c>
       <c r="R20" t="n">
-        <v>27.9</v>
+        <v>27.01</v>
       </c>
       <c r="S20" t="n">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="T20" t="n">
-        <v>8.57</v>
+        <v>5.1</v>
       </c>
       <c r="U20" t="n">
-        <v>2.79</v>
+        <v>3.46</v>
       </c>
       <c r="V20" t="n">
-        <v>15.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>敦陽科</t>
+          <t>茂達</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -1929,69 +1929,69 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6.3</v>
+        <v>2.6</v>
       </c>
       <c r="F21" t="n">
-        <v>10.4</v>
+        <v>14.9</v>
       </c>
       <c r="G21" t="n">
         <v>24.2</v>
       </c>
       <c r="H21" t="n">
-        <v>23.9</v>
+        <v>37</v>
       </c>
       <c r="I21" t="n">
-        <v>11.8</v>
+        <v>18.3</v>
       </c>
       <c r="J21" t="n">
-        <v>10.2</v>
+        <v>16.3</v>
       </c>
       <c r="K21" t="n">
-        <v>8.390000000000001</v>
+        <v>14.12</v>
       </c>
       <c r="L21" t="n">
-        <v>29.9</v>
+        <v>28.8</v>
       </c>
       <c r="M21" t="n">
-        <v>64.40000000000001</v>
+        <v>39.7</v>
       </c>
       <c r="N21" t="n">
-        <v>135</v>
+        <v>215</v>
       </c>
       <c r="O21" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="P21" t="n">
-        <v>10.8</v>
+        <v>13.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>154.5</v>
+        <v>394</v>
       </c>
       <c r="R21" t="n">
-        <v>18.41</v>
+        <v>27.9</v>
       </c>
       <c r="S21" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="T21" t="n">
-        <v>5.5</v>
+        <v>8.57</v>
       </c>
       <c r="U21" t="n">
-        <v>5.05</v>
+        <v>2.79</v>
       </c>
       <c r="V21" t="n">
-        <v>16.4</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>敦陽科</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -2001,58 +2001,58 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1</v>
+        <v>10.4</v>
       </c>
       <c r="G22" t="n">
         <v>24.2</v>
       </c>
       <c r="H22" t="n">
-        <v>36</v>
+        <v>23.9</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>11.8</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5</v>
+        <v>10.2</v>
       </c>
       <c r="K22" t="n">
-        <v>6.96</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>17.5</v>
+        <v>29.9</v>
       </c>
       <c r="M22" t="n">
-        <v>88.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="O22" t="n">
-        <v>6.49</v>
+        <v>1.33</v>
       </c>
       <c r="P22" t="n">
-        <v>62.8</v>
+        <v>10.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>188</v>
+        <v>154.5</v>
       </c>
       <c r="R22" t="n">
-        <v>27.01</v>
+        <v>18.41</v>
       </c>
       <c r="S22" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="T22" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="U22" t="n">
-        <v>3.46</v>
+        <v>5.05</v>
       </c>
       <c r="V22" t="n">
-        <v>7.4</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="23">
@@ -2418,12 +2418,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>大樹</t>
+          <t>長聖</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -2433,69 +2433,69 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>13.8</v>
+        <v>23.4</v>
       </c>
       <c r="F28" t="n">
-        <v>3.9</v>
+        <v>49.4</v>
       </c>
       <c r="G28" t="n">
         <v>21.9</v>
       </c>
       <c r="H28" t="n">
-        <v>28.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>3.3</v>
+        <v>44.9</v>
       </c>
       <c r="J28" t="n">
-        <v>2.9</v>
+        <v>48.4</v>
       </c>
       <c r="K28" t="n">
-        <v>3.91</v>
+        <v>5.27</v>
       </c>
       <c r="L28" t="n">
-        <v>15</v>
+        <v>16.7</v>
       </c>
       <c r="M28" t="n">
-        <v>73.5</v>
+        <v>22.4</v>
       </c>
       <c r="N28" t="n">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="O28" t="n">
-        <v>2.05</v>
+        <v>1.16</v>
       </c>
       <c r="P28" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>74.3</v>
+        <v>142.5</v>
       </c>
       <c r="R28" t="n">
-        <v>19</v>
+        <v>27.04</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T28" t="n">
-        <v>3.12</v>
+        <v>4.87</v>
       </c>
       <c r="U28" t="n">
-        <v>5.06</v>
+        <v>2.81</v>
       </c>
       <c r="V28" t="n">
-        <v>2.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>長聖</t>
+          <t>大樹</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -2505,58 +2505,58 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>23.4</v>
+        <v>13.8</v>
       </c>
       <c r="F29" t="n">
-        <v>49.4</v>
+        <v>3.9</v>
       </c>
       <c r="G29" t="n">
         <v>21.9</v>
       </c>
       <c r="H29" t="n">
-        <v>73.09999999999999</v>
+        <v>28.7</v>
       </c>
       <c r="I29" t="n">
-        <v>44.9</v>
+        <v>3.3</v>
       </c>
       <c r="J29" t="n">
-        <v>48.4</v>
+        <v>2.9</v>
       </c>
       <c r="K29" t="n">
-        <v>5.27</v>
+        <v>3.91</v>
       </c>
       <c r="L29" t="n">
-        <v>16.7</v>
+        <v>15</v>
       </c>
       <c r="M29" t="n">
-        <v>22.4</v>
+        <v>73.5</v>
       </c>
       <c r="N29" t="n">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="O29" t="n">
-        <v>1.16</v>
+        <v>2.05</v>
       </c>
       <c r="P29" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="Q29" t="n">
-        <v>142.5</v>
+        <v>74.3</v>
       </c>
       <c r="R29" t="n">
-        <v>27.04</v>
+        <v>19</v>
       </c>
       <c r="S29" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T29" t="n">
-        <v>4.87</v>
+        <v>3.12</v>
       </c>
       <c r="U29" t="n">
-        <v>2.81</v>
+        <v>5.06</v>
       </c>
       <c r="V29" t="n">
-        <v>25</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="30">
@@ -3642,12 +3642,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>緯軟</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -3657,69 +3657,69 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>17</v>
+        <v>2.8</v>
       </c>
       <c r="F45" t="n">
-        <v>6.1</v>
+        <v>15.4</v>
       </c>
       <c r="G45" t="n">
         <v>17.6</v>
       </c>
       <c r="H45" t="n">
-        <v>16.5</v>
+        <v>27</v>
       </c>
       <c r="I45" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>5.5</v>
+        <v>14.3</v>
       </c>
       <c r="K45" t="n">
-        <v>9.26</v>
+        <v>6.07</v>
       </c>
       <c r="L45" t="n">
-        <v>15.9</v>
+        <v>17.9</v>
       </c>
       <c r="M45" t="n">
-        <v>34.8</v>
+        <v>39.6</v>
       </c>
       <c r="N45" t="n">
-        <v>266</v>
+        <v>183</v>
       </c>
       <c r="O45" t="n">
-        <v>0.53</v>
+        <v>1.71</v>
       </c>
       <c r="P45" t="n">
-        <v>3.4</v>
+        <v>10.4</v>
       </c>
       <c r="Q45" t="n">
-        <v>132.5</v>
+        <v>155</v>
       </c>
       <c r="R45" t="n">
-        <v>14.31</v>
+        <v>25.54</v>
       </c>
       <c r="S45" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="T45" t="n">
-        <v>2.22</v>
+        <v>4.56</v>
       </c>
       <c r="U45" t="n">
-        <v>3.88</v>
+        <v>3.23</v>
       </c>
       <c r="V45" t="n">
-        <v>29.2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>緯軟</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -3729,58 +3729,58 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2.8</v>
+        <v>17</v>
       </c>
       <c r="F46" t="n">
-        <v>15.4</v>
+        <v>6.1</v>
       </c>
       <c r="G46" t="n">
         <v>17.6</v>
       </c>
       <c r="H46" t="n">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="J46" t="n">
-        <v>14.3</v>
+        <v>5.5</v>
       </c>
       <c r="K46" t="n">
-        <v>6.07</v>
+        <v>9.26</v>
       </c>
       <c r="L46" t="n">
-        <v>17.9</v>
+        <v>15.9</v>
       </c>
       <c r="M46" t="n">
-        <v>39.6</v>
+        <v>34.8</v>
       </c>
       <c r="N46" t="n">
-        <v>183</v>
+        <v>266</v>
       </c>
       <c r="O46" t="n">
-        <v>1.71</v>
+        <v>0.53</v>
       </c>
       <c r="P46" t="n">
-        <v>10.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q46" t="n">
-        <v>155</v>
+        <v>132.5</v>
       </c>
       <c r="R46" t="n">
-        <v>25.54</v>
+        <v>14.31</v>
       </c>
       <c r="S46" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="T46" t="n">
-        <v>4.56</v>
+        <v>2.22</v>
       </c>
       <c r="U46" t="n">
-        <v>3.23</v>
+        <v>3.88</v>
       </c>
       <c r="V46" t="n">
-        <v>19</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="47">
@@ -3858,12 +3858,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -3873,58 +3873,58 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>15.2</v>
+        <v>11.1</v>
       </c>
       <c r="F48" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="G48" t="n">
         <v>17.1</v>
       </c>
       <c r="H48" t="n">
-        <v>35.5</v>
+        <v>25.9</v>
       </c>
       <c r="I48" t="n">
-        <v>16.4</v>
+        <v>18.1</v>
       </c>
       <c r="J48" t="n">
-        <v>13.3</v>
+        <v>14.8</v>
       </c>
       <c r="K48" t="n">
-        <v>27.11</v>
+        <v>8.23</v>
       </c>
       <c r="L48" t="n">
-        <v>22.3</v>
+        <v>18.6</v>
       </c>
       <c r="M48" t="n">
-        <v>47.8</v>
+        <v>55.1</v>
       </c>
       <c r="N48" t="n">
-        <v>195</v>
+        <v>111</v>
       </c>
       <c r="O48" t="n">
-        <v>1.28</v>
+        <v>2.74</v>
       </c>
       <c r="P48" t="n">
-        <v>535.6</v>
+        <v>107</v>
       </c>
       <c r="Q48" t="n">
-        <v>2150</v>
+        <v>181</v>
       </c>
       <c r="R48" t="n">
-        <v>79.31</v>
+        <v>21.99</v>
       </c>
       <c r="S48" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="T48" t="n">
-        <v>18.64</v>
+        <v>4.15</v>
       </c>
       <c r="U48" t="n">
-        <v>0.54</v>
+        <v>3.31</v>
       </c>
       <c r="V48" t="n">
-        <v>43.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="49">
@@ -4002,12 +4002,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -4017,58 +4017,58 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>11.1</v>
+        <v>15.2</v>
       </c>
       <c r="F50" t="n">
-        <v>11.9</v>
+        <v>10</v>
       </c>
       <c r="G50" t="n">
         <v>17.1</v>
       </c>
       <c r="H50" t="n">
-        <v>25.9</v>
+        <v>35.5</v>
       </c>
       <c r="I50" t="n">
-        <v>18.1</v>
+        <v>16.4</v>
       </c>
       <c r="J50" t="n">
-        <v>14.8</v>
+        <v>13.3</v>
       </c>
       <c r="K50" t="n">
-        <v>8.23</v>
+        <v>27.11</v>
       </c>
       <c r="L50" t="n">
-        <v>18.6</v>
+        <v>22.3</v>
       </c>
       <c r="M50" t="n">
-        <v>55.1</v>
+        <v>47.8</v>
       </c>
       <c r="N50" t="n">
-        <v>111</v>
+        <v>195</v>
       </c>
       <c r="O50" t="n">
-        <v>2.74</v>
+        <v>1.28</v>
       </c>
       <c r="P50" t="n">
-        <v>107</v>
+        <v>535.6</v>
       </c>
       <c r="Q50" t="n">
-        <v>181</v>
+        <v>2150</v>
       </c>
       <c r="R50" t="n">
-        <v>21.99</v>
+        <v>79.31</v>
       </c>
       <c r="S50" t="n">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="T50" t="n">
-        <v>4.15</v>
+        <v>18.64</v>
       </c>
       <c r="U50" t="n">
-        <v>3.31</v>
+        <v>0.54</v>
       </c>
       <c r="V50" t="n">
-        <v>3.6</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="51">
@@ -4578,12 +4578,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>閎康</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -4593,58 +4593,58 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>-0.8</v>
+        <v>13.3</v>
       </c>
       <c r="F58" t="n">
-        <v>15.7</v>
+        <v>13.5</v>
       </c>
       <c r="G58" t="n">
         <v>15.8</v>
       </c>
       <c r="H58" t="n">
-        <v>18.3</v>
+        <v>30</v>
       </c>
       <c r="I58" t="n">
-        <v>5.6</v>
+        <v>11.4</v>
       </c>
       <c r="J58" t="n">
-        <v>28.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>8.640000000000001</v>
+        <v>7.57</v>
       </c>
       <c r="L58" t="n">
-        <v>21.8</v>
+        <v>9.9</v>
       </c>
       <c r="M58" t="n">
-        <v>25.7</v>
+        <v>46.1</v>
       </c>
       <c r="N58" t="n">
-        <v>377</v>
+        <v>200</v>
       </c>
       <c r="O58" t="n">
-        <v>0.01</v>
+        <v>3.9</v>
       </c>
       <c r="P58" t="n">
-        <v>-2.1</v>
+        <v>13.6</v>
       </c>
       <c r="Q58" t="n">
-        <v>870</v>
+        <v>304</v>
       </c>
       <c r="R58" t="n">
-        <v>100.69</v>
+        <v>40.16</v>
       </c>
       <c r="S58" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="T58" t="n">
-        <v>21.95</v>
+        <v>4.01</v>
       </c>
       <c r="U58" t="n">
-        <v>0.4</v>
+        <v>1.48</v>
       </c>
       <c r="V58" t="n">
-        <v>30</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="59">
@@ -4722,12 +4722,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>閎康</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -4737,58 +4737,58 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>13.3</v>
+        <v>-0.8</v>
       </c>
       <c r="F60" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="G60" t="n">
         <v>15.8</v>
       </c>
       <c r="H60" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="I60" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J60" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="K60" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="L60" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="M60" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="N60" t="n">
+        <v>377</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P60" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>870</v>
+      </c>
+      <c r="R60" t="n">
+        <v>100.69</v>
+      </c>
+      <c r="S60" t="n">
+        <v>94</v>
+      </c>
+      <c r="T60" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V60" t="n">
         <v>30</v>
-      </c>
-      <c r="I60" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J60" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="K60" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="L60" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="M60" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="N60" t="n">
-        <v>200</v>
-      </c>
-      <c r="O60" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P60" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>304</v>
-      </c>
-      <c r="R60" t="n">
-        <v>40.16</v>
-      </c>
-      <c r="S60" t="n">
-        <v>97</v>
-      </c>
-      <c r="T60" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V60" t="n">
-        <v>26.9</v>
       </c>
     </row>
     <row r="61">
@@ -5514,12 +5514,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>台特化</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -5529,69 +5529,69 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>126.1</v>
+        <v>10.9</v>
       </c>
       <c r="F71" t="n">
-        <v>41.8</v>
+        <v>23.2</v>
       </c>
       <c r="G71" t="n">
         <v>14.1</v>
       </c>
       <c r="H71" t="n">
-        <v>53.1</v>
+        <v>39.8</v>
       </c>
       <c r="I71" t="n">
-        <v>42.8</v>
+        <v>21.3</v>
       </c>
       <c r="J71" t="n">
-        <v>36.1</v>
+        <v>26.7</v>
       </c>
       <c r="K71" t="n">
-        <v>4.84</v>
+        <v>7.68</v>
       </c>
       <c r="L71" t="n">
-        <v>20.7</v>
+        <v>14.7</v>
       </c>
       <c r="M71" t="n">
-        <v>42.3</v>
+        <v>36</v>
       </c>
       <c r="N71" t="n">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="O71" t="n">
-        <v>1.36</v>
+        <v>0.63</v>
       </c>
       <c r="P71" t="n">
-        <v>8.800000000000001</v>
+        <v>-1.2</v>
       </c>
       <c r="Q71" t="n">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="R71" t="n">
-        <v>58.47</v>
+        <v>38.15</v>
       </c>
       <c r="S71" t="n">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="T71" t="n">
-        <v>12.02</v>
+        <v>5.71</v>
       </c>
       <c r="U71" t="n">
-        <v>1.06</v>
+        <v>1.57</v>
       </c>
       <c r="V71" t="n">
-        <v>241.2</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>台特化</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -5601,58 +5601,58 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>10.9</v>
+        <v>126.1</v>
       </c>
       <c r="F72" t="n">
-        <v>23.2</v>
+        <v>41.8</v>
       </c>
       <c r="G72" t="n">
         <v>14.1</v>
       </c>
       <c r="H72" t="n">
-        <v>39.8</v>
+        <v>53.1</v>
       </c>
       <c r="I72" t="n">
-        <v>21.3</v>
+        <v>42.8</v>
       </c>
       <c r="J72" t="n">
-        <v>26.7</v>
+        <v>36.1</v>
       </c>
       <c r="K72" t="n">
-        <v>7.68</v>
+        <v>4.84</v>
       </c>
       <c r="L72" t="n">
-        <v>14.7</v>
+        <v>20.7</v>
       </c>
       <c r="M72" t="n">
-        <v>36</v>
+        <v>42.3</v>
       </c>
       <c r="N72" t="n">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="O72" t="n">
-        <v>0.63</v>
+        <v>1.36</v>
       </c>
       <c r="P72" t="n">
-        <v>-1.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q72" t="n">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="R72" t="n">
-        <v>38.15</v>
+        <v>58.47</v>
       </c>
       <c r="S72" t="n">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="T72" t="n">
-        <v>5.71</v>
+        <v>12.02</v>
       </c>
       <c r="U72" t="n">
-        <v>1.57</v>
+        <v>1.06</v>
       </c>
       <c r="V72" t="n">
-        <v>16.6</v>
+        <v>241.2</v>
       </c>
     </row>
     <row r="73">
@@ -6666,12 +6666,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>世禾</t>
+          <t>遠雄港</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -6681,69 +6681,69 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>8.9</v>
+        <v>13</v>
       </c>
       <c r="F87" t="n">
-        <v>15.7</v>
+        <v>28.5</v>
       </c>
       <c r="G87" t="n">
         <v>10.5</v>
       </c>
       <c r="H87" t="n">
-        <v>35.6</v>
+        <v>50.4</v>
       </c>
       <c r="I87" t="n">
-        <v>17.5</v>
+        <v>39.2</v>
       </c>
       <c r="J87" t="n">
-        <v>16.3</v>
+        <v>27</v>
       </c>
       <c r="K87" t="n">
-        <v>8.69</v>
+        <v>3.24</v>
       </c>
       <c r="L87" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="M87" t="n">
-        <v>19.3</v>
+        <v>58</v>
       </c>
       <c r="N87" t="n">
-        <v>434</v>
+        <v>48</v>
       </c>
       <c r="O87" t="n">
-        <v>-0.79</v>
+        <v>1.91</v>
       </c>
       <c r="P87" t="n">
-        <v>-6.2</v>
+        <v>18.5</v>
       </c>
       <c r="Q87" t="n">
-        <v>212.5</v>
+        <v>52.2</v>
       </c>
       <c r="R87" t="n">
-        <v>24.45</v>
+        <v>16.11</v>
       </c>
       <c r="S87" t="n">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="T87" t="n">
-        <v>2.57</v>
+        <v>1.69</v>
       </c>
       <c r="U87" t="n">
-        <v>2.26</v>
+        <v>3.45</v>
       </c>
       <c r="V87" t="n">
-        <v>21.5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>遠雄港</t>
+          <t>世禾</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -6753,58 +6753,58 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>13</v>
+        <v>8.9</v>
       </c>
       <c r="F88" t="n">
-        <v>28.5</v>
+        <v>15.7</v>
       </c>
       <c r="G88" t="n">
         <v>10.5</v>
       </c>
       <c r="H88" t="n">
-        <v>50.4</v>
+        <v>35.6</v>
       </c>
       <c r="I88" t="n">
-        <v>39.2</v>
+        <v>17.5</v>
       </c>
       <c r="J88" t="n">
-        <v>27</v>
+        <v>16.3</v>
       </c>
       <c r="K88" t="n">
-        <v>3.24</v>
+        <v>8.69</v>
       </c>
       <c r="L88" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="M88" t="n">
-        <v>58</v>
+        <v>19.3</v>
       </c>
       <c r="N88" t="n">
-        <v>48</v>
+        <v>434</v>
       </c>
       <c r="O88" t="n">
-        <v>1.91</v>
+        <v>-0.79</v>
       </c>
       <c r="P88" t="n">
-        <v>18.5</v>
+        <v>-6.2</v>
       </c>
       <c r="Q88" t="n">
-        <v>52.2</v>
+        <v>212.5</v>
       </c>
       <c r="R88" t="n">
-        <v>16.11</v>
+        <v>24.45</v>
       </c>
       <c r="S88" t="n">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="T88" t="n">
-        <v>1.69</v>
+        <v>2.57</v>
       </c>
       <c r="U88" t="n">
-        <v>3.45</v>
+        <v>2.26</v>
       </c>
       <c r="V88" t="n">
-        <v>39</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="89">
@@ -7950,12 +7950,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>先進光</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -7965,69 +7965,69 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4.3</v>
+        <v>-2.9</v>
       </c>
       <c r="F105" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G105" t="n">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
       <c r="H105" t="n">
-        <v>17</v>
+        <v>29.3</v>
       </c>
       <c r="I105" t="n">
-        <v>-2</v>
+        <v>7.5</v>
       </c>
       <c r="J105" t="n">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="K105" t="n">
-        <v>-1.84</v>
+        <v>4.58</v>
       </c>
       <c r="L105" t="n">
-        <v>-7.2</v>
+        <v>4</v>
       </c>
       <c r="M105" t="n">
-        <v>65.7</v>
+        <v>31.3</v>
       </c>
       <c r="N105" t="n">
-        <v>94</v>
+        <v>229</v>
       </c>
       <c r="O105" t="n">
-        <v>-0.67</v>
+        <v>3.06</v>
       </c>
       <c r="P105" t="n">
-        <v>-6.6</v>
+        <v>29.5</v>
       </c>
       <c r="Q105" t="n">
-        <v>129</v>
+        <v>343.5</v>
       </c>
       <c r="R105" t="n">
-        <v>65.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="S105" t="n">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="T105" t="n">
-        <v>8.01</v>
+        <v>3.16</v>
       </c>
       <c r="U105" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="V105" t="n">
-        <v>-13.9</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>先進光</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -8037,69 +8037,69 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.2</v>
+        <v>4.3</v>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="G106" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="H106" t="n">
-        <v>6.6</v>
+        <v>17</v>
       </c>
       <c r="I106" t="n">
-        <v>4.8</v>
+        <v>-2</v>
       </c>
       <c r="J106" t="n">
-        <v>4.1</v>
+        <v>-6</v>
       </c>
       <c r="K106" t="n">
-        <v>2.79</v>
+        <v>-1.84</v>
       </c>
       <c r="L106" t="n">
-        <v>7</v>
+        <v>-7.2</v>
       </c>
       <c r="M106" t="n">
-        <v>17.9</v>
+        <v>65.7</v>
       </c>
       <c r="N106" t="n">
-        <v>451</v>
+        <v>94</v>
       </c>
       <c r="O106" t="n">
-        <v>1.85</v>
+        <v>-0.67</v>
       </c>
       <c r="P106" t="n">
-        <v>409.6</v>
+        <v>-6.6</v>
       </c>
       <c r="Q106" t="n">
-        <v>54</v>
+        <v>129</v>
       </c>
       <c r="R106" t="n">
-        <v>19.35</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="S106" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="T106" t="n">
-        <v>1.36</v>
+        <v>8.01</v>
       </c>
       <c r="U106" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="V106" t="n">
-        <v>26.9</v>
+        <v>-13.9</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>健喬</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -8109,69 +8109,69 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>17.6</v>
+        <v>3</v>
       </c>
       <c r="F107" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G107" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H107" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I107" t="n">
         <v>8.9</v>
       </c>
-      <c r="G107" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H107" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="I107" t="n">
-        <v>11.8</v>
-      </c>
       <c r="J107" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="K107" t="n">
-        <v>1.61</v>
+        <v>2.39</v>
       </c>
       <c r="L107" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="M107" t="n">
-        <v>28.3</v>
+        <v>36.6</v>
       </c>
       <c r="N107" t="n">
-        <v>260</v>
+        <v>211</v>
       </c>
       <c r="O107" t="n">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="P107" t="n">
-        <v>2.9</v>
+        <v>23.6</v>
       </c>
       <c r="Q107" t="n">
-        <v>30.9</v>
+        <v>72.2</v>
       </c>
       <c r="R107" t="n">
-        <v>19.22</v>
+        <v>30.21</v>
       </c>
       <c r="S107" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="T107" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="U107" t="n">
-        <v>5.33</v>
+        <v>2.86</v>
       </c>
       <c r="V107" t="n">
-        <v>12.9</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>奈米醫材</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -8181,69 +8181,69 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>30.5</v>
+        <v>0.2</v>
       </c>
       <c r="F108" t="n">
-        <v>9.300000000000001</v>
+        <v>3</v>
       </c>
       <c r="G108" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="H108" t="n">
-        <v>58.4</v>
+        <v>6.6</v>
       </c>
       <c r="I108" t="n">
-        <v>10.2</v>
+        <v>4.8</v>
       </c>
       <c r="J108" t="n">
-        <v>-1.2</v>
+        <v>4.1</v>
       </c>
       <c r="K108" t="n">
-        <v>0.85</v>
+        <v>2.79</v>
       </c>
       <c r="L108" t="n">
-        <v>-0.5</v>
+        <v>7</v>
       </c>
       <c r="M108" t="n">
-        <v>37.5</v>
+        <v>17.9</v>
       </c>
       <c r="N108" t="n">
-        <v>207</v>
+        <v>451</v>
       </c>
       <c r="O108" t="n">
-        <v>-1.67</v>
+        <v>1.85</v>
       </c>
       <c r="P108" t="n">
-        <v>-0.2</v>
+        <v>409.6</v>
       </c>
       <c r="Q108" t="n">
-        <v>72.90000000000001</v>
+        <v>54</v>
       </c>
       <c r="R108" t="n">
-        <v>85.76000000000001</v>
+        <v>19.35</v>
       </c>
       <c r="S108" t="n">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="T108" t="n">
-        <v>1.84</v>
+        <v>1.36</v>
       </c>
       <c r="U108" t="n">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="V108" t="n">
-        <v>43.3</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>健喬</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -8253,69 +8253,69 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4</v>
+        <v>17.6</v>
       </c>
       <c r="F109" t="n">
-        <v>3.7</v>
+        <v>8.9</v>
       </c>
       <c r="G109" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="H109" t="n">
-        <v>47.6</v>
+        <v>42.8</v>
       </c>
       <c r="I109" t="n">
-        <v>29.9</v>
+        <v>11.8</v>
       </c>
       <c r="J109" t="n">
-        <v>25</v>
+        <v>9.4</v>
       </c>
       <c r="K109" t="n">
-        <v>7.64</v>
+        <v>1.61</v>
       </c>
       <c r="L109" t="n">
-        <v>16.6</v>
+        <v>5.9</v>
       </c>
       <c r="M109" t="n">
-        <v>25.3</v>
+        <v>28.3</v>
       </c>
       <c r="N109" t="n">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="O109" t="n">
-        <v>1.13</v>
+        <v>0.76</v>
       </c>
       <c r="P109" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q109" t="n">
-        <v>2375</v>
+        <v>30.9</v>
       </c>
       <c r="R109" t="n">
-        <v>310.86</v>
+        <v>19.22</v>
       </c>
       <c r="S109" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="T109" t="n">
-        <v>51.83</v>
+        <v>1.76</v>
       </c>
       <c r="U109" t="n">
-        <v>0.17</v>
+        <v>5.33</v>
       </c>
       <c r="V109" t="n">
-        <v>118.8</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>奈米醫材</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -8325,69 +8325,69 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>15.3</v>
+        <v>30.5</v>
       </c>
       <c r="F110" t="n">
-        <v>4.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G110" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="H110" t="n">
-        <v>17.8</v>
+        <v>58.4</v>
       </c>
       <c r="I110" t="n">
-        <v>2.6</v>
+        <v>10.2</v>
       </c>
       <c r="J110" t="n">
-        <v>0.1</v>
+        <v>-1.2</v>
       </c>
       <c r="K110" t="n">
-        <v>-0.14</v>
+        <v>0.85</v>
       </c>
       <c r="L110" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="M110" t="n">
-        <v>59.7</v>
+        <v>37.5</v>
       </c>
       <c r="N110" t="n">
-        <v>167</v>
+        <v>207</v>
       </c>
       <c r="O110" t="n">
-        <v>7.24</v>
+        <v>-1.67</v>
       </c>
       <c r="P110" t="n">
-        <v>-15.2</v>
+        <v>-0.2</v>
       </c>
       <c r="Q110" t="n">
-        <v>525</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="R110" t="n">
-        <v>2019.23</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="S110" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="T110" t="n">
-        <v>9.34</v>
+        <v>1.84</v>
       </c>
       <c r="U110" t="n">
-        <v>0.04</v>
+        <v>1.78</v>
       </c>
       <c r="V110" t="n">
-        <v>4.9</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>矽統</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -8397,69 +8397,69 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>83.3</v>
+        <v>4</v>
       </c>
       <c r="F111" t="n">
-        <v>114.5</v>
+        <v>3.7</v>
       </c>
       <c r="G111" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="H111" t="n">
-        <v>28.7</v>
+        <v>47.6</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6</v>
+        <v>29.9</v>
       </c>
       <c r="J111" t="n">
-        <v>30.7</v>
+        <v>25</v>
       </c>
       <c r="K111" t="n">
-        <v>1.7</v>
+        <v>7.64</v>
       </c>
       <c r="L111" t="n">
-        <v>4.2</v>
+        <v>16.6</v>
       </c>
       <c r="M111" t="n">
-        <v>9.199999999999999</v>
+        <v>25.3</v>
       </c>
       <c r="N111" t="n">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="O111" t="n">
-        <v>0.6</v>
+        <v>1.13</v>
       </c>
       <c r="P111" t="n">
-        <v>4.8</v>
+        <v>6.9</v>
       </c>
       <c r="Q111" t="n">
-        <v>69.09999999999999</v>
+        <v>2375</v>
       </c>
       <c r="R111" t="n">
-        <v>40.65</v>
+        <v>310.86</v>
       </c>
       <c r="S111" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="T111" t="n">
-        <v>1.75</v>
+        <v>51.83</v>
       </c>
       <c r="U111" t="n">
-        <v>0.87</v>
+        <v>0.17</v>
       </c>
       <c r="V111" t="n">
-        <v>88.8</v>
+        <v>118.8</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>上詮</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -8469,69 +8469,69 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>-1.3</v>
+        <v>15.3</v>
       </c>
       <c r="F112" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="G112" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="H112" t="n">
-        <v>14.5</v>
+        <v>17.8</v>
       </c>
       <c r="I112" t="n">
-        <v>-10.6</v>
+        <v>2.6</v>
       </c>
       <c r="J112" t="n">
-        <v>-6.7</v>
+        <v>0.1</v>
       </c>
       <c r="K112" t="n">
-        <v>-0.83</v>
+        <v>-0.14</v>
       </c>
       <c r="L112" t="n">
-        <v>-1.6</v>
+        <v>0.5</v>
       </c>
       <c r="M112" t="n">
-        <v>9.1</v>
+        <v>59.7</v>
       </c>
       <c r="N112" t="n">
-        <v>1107</v>
+        <v>167</v>
       </c>
       <c r="O112" t="n">
-        <v>0.97</v>
+        <v>7.24</v>
       </c>
       <c r="P112" t="n">
-        <v>-2.4</v>
+        <v>-15.2</v>
       </c>
       <c r="Q112" t="n">
-        <v>902</v>
+        <v>525</v>
       </c>
       <c r="R112" t="n">
-        <v>5637.5</v>
+        <v>2019.23</v>
       </c>
       <c r="S112" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="T112" t="n">
-        <v>14.11</v>
+        <v>9.34</v>
       </c>
       <c r="U112" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="V112" t="n">
-        <v>-24.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>精確</t>
+          <t>矽統</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -8541,69 +8541,69 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>54.8</v>
+        <v>83.3</v>
       </c>
       <c r="F113" t="n">
-        <v>0.4</v>
+        <v>114.5</v>
       </c>
       <c r="G113" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="H113" t="n">
-        <v>11.8</v>
+        <v>28.7</v>
       </c>
       <c r="I113" t="n">
-        <v>1.8</v>
+        <v>-0.6</v>
       </c>
       <c r="J113" t="n">
-        <v>2.1</v>
+        <v>30.7</v>
       </c>
       <c r="K113" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="L113" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="M113" t="n">
-        <v>62.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="N113" t="n">
-        <v>96</v>
+        <v>298</v>
       </c>
       <c r="O113" t="n">
-        <v>5.72</v>
+        <v>0.6</v>
       </c>
       <c r="P113" t="n">
-        <v>-0.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q113" t="n">
-        <v>84.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="R113" t="n">
-        <v>69.34</v>
+        <v>40.65</v>
       </c>
       <c r="S113" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="T113" t="n">
-        <v>3.17</v>
+        <v>1.75</v>
       </c>
       <c r="U113" t="n">
-        <v>1.18</v>
+        <v>0.87</v>
       </c>
       <c r="V113" t="n">
-        <v>21.9</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>訊連</t>
+          <t>上詮</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -8613,197 +8613,213 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>11.7</v>
+        <v>-1.3</v>
       </c>
       <c r="F114" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="G114" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="H114" t="n">
-        <v>84.3</v>
+        <v>14.5</v>
       </c>
       <c r="I114" t="n">
-        <v>15.3</v>
+        <v>-10.6</v>
       </c>
       <c r="J114" t="n">
-        <v>11.6</v>
+        <v>-6.7</v>
       </c>
       <c r="K114" t="n">
-        <v>3.68</v>
+        <v>-0.83</v>
       </c>
       <c r="L114" t="n">
-        <v>6.1</v>
+        <v>-1.6</v>
       </c>
       <c r="M114" t="n">
-        <v>22.2</v>
+        <v>9.1</v>
       </c>
       <c r="N114" t="n">
-        <v>273</v>
+        <v>1107</v>
       </c>
       <c r="O114" t="n">
-        <v>-2.09</v>
+        <v>0.97</v>
       </c>
       <c r="P114" t="n">
-        <v>-6.1</v>
+        <v>-2.4</v>
       </c>
       <c r="Q114" t="n">
-        <v>69</v>
+        <v>902</v>
       </c>
       <c r="R114" t="n">
-        <v>18.75</v>
+        <v>5637.5</v>
       </c>
       <c r="S114" t="n">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="T114" t="n">
-        <v>1.14</v>
+        <v>14.11</v>
       </c>
       <c r="U114" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="V114" t="n">
-        <v>-14.8</v>
+        <v>-24.8</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>🏦</t>
-        </is>
-      </c>
+          <t>精確</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>24</v>
-      </c>
-      <c r="F115" t="inlineStr"/>
+        <v>54.8</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.4</v>
+      </c>
       <c r="G115" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
+        <v>1.4</v>
+      </c>
+      <c r="H115" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J115" t="n">
+        <v>2.1</v>
+      </c>
       <c r="K115" t="n">
-        <v>1.58</v>
+        <v>1.22</v>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M115" t="n">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
+        <v>62.1</v>
+      </c>
+      <c r="N115" t="n">
+        <v>96</v>
+      </c>
+      <c r="O115" t="n">
+        <v>5.72</v>
+      </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="Q115" t="n">
-        <v>32</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="R115" t="n">
-        <v>16.78</v>
+        <v>69.34</v>
       </c>
       <c r="S115" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="T115" t="n">
-        <v>1.41</v>
+        <v>3.17</v>
       </c>
       <c r="U115" t="n">
-        <v>3.43</v>
+        <v>1.18</v>
       </c>
       <c r="V115" t="n">
-        <v>117.9</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>永豐金</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>🏦</t>
-        </is>
-      </c>
+          <t>訊連</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>13</v>
-      </c>
-      <c r="F116" t="inlineStr"/>
+        <v>11.7</v>
+      </c>
+      <c r="F116" t="n">
+        <v>3.2</v>
+      </c>
       <c r="G116" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+        <v>0.6</v>
+      </c>
+      <c r="H116" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="I116" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J116" t="n">
+        <v>11.6</v>
+      </c>
       <c r="K116" t="n">
-        <v>1.4</v>
+        <v>3.68</v>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="M116" t="n">
-        <v>93</v>
-      </c>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
+        <v>22.2</v>
+      </c>
+      <c r="N116" t="n">
+        <v>273</v>
+      </c>
+      <c r="O116" t="n">
+        <v>-2.09</v>
+      </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>-6.1</v>
       </c>
       <c r="Q116" t="n">
-        <v>39.8</v>
+        <v>69</v>
       </c>
       <c r="R116" t="n">
-        <v>20.2</v>
+        <v>18.75</v>
       </c>
       <c r="S116" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="T116" t="n">
-        <v>2.17</v>
+        <v>1.14</v>
       </c>
       <c r="U116" t="n">
-        <v>3.27</v>
+        <v>5.22</v>
       </c>
       <c r="V116" t="n">
-        <v>82.7</v>
+        <v>-14.8</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -8817,7 +8833,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>-24</v>
+        <v>8</v>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="n">
@@ -8827,13 +8843,13 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>91.2</v>
+        <v>94.5</v>
       </c>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
@@ -8841,33 +8857,33 @@
         <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>30.4</v>
+        <v>37.6</v>
       </c>
       <c r="R117" t="n">
-        <v>17.44</v>
+        <v>19.79</v>
       </c>
       <c r="S117" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T117" t="n">
-        <v>1.54</v>
+        <v>2.15</v>
       </c>
       <c r="U117" t="n">
-        <v>3.25</v>
+        <v>3.86</v>
       </c>
       <c r="V117" t="n">
-        <v>-172.7</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -8881,7 +8897,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>-5.9</v>
+        <v>13</v>
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
@@ -8891,13 +8907,13 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="n">
-        <v>5.37</v>
+        <v>1.4</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>92.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
@@ -8905,33 +8921,33 @@
         <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>138.5</v>
+        <v>39.8</v>
       </c>
       <c r="R118" t="n">
-        <v>16.55</v>
+        <v>20.2</v>
       </c>
       <c r="S118" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="T118" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="U118" t="n">
-        <v>3.08</v>
+        <v>3.27</v>
       </c>
       <c r="V118" t="n">
-        <v>-300.3</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8945,7 +8961,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>8</v>
+        <v>1.9</v>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
@@ -8955,13 +8971,13 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="n">
-        <v>1.51</v>
+        <v>2.15</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>94.5</v>
+        <v>91.7</v>
       </c>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
@@ -8969,33 +8985,33 @@
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>37.6</v>
+        <v>68.8</v>
       </c>
       <c r="R119" t="n">
-        <v>19.79</v>
+        <v>25.11</v>
       </c>
       <c r="S119" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="T119" t="n">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="U119" t="n">
-        <v>3.86</v>
+        <v>3.24</v>
       </c>
       <c r="V119" t="n">
-        <v>58.3</v>
+        <v>227.3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>台中銀</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -9008,7 +9024,9 @@
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
+      <c r="E120" t="n">
+        <v>-5.9</v>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
         <v>0</v>
@@ -9017,13 +9035,13 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="n">
-        <v>1.14</v>
+        <v>5.37</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>90.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
@@ -9031,33 +9049,33 @@
         <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>19.6</v>
+        <v>138.5</v>
       </c>
       <c r="R120" t="n">
-        <v>12.84</v>
+        <v>16.55</v>
       </c>
       <c r="S120" t="n">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="T120" t="n">
-        <v>1.26</v>
+        <v>2.11</v>
       </c>
       <c r="U120" t="n">
-        <v>5.39</v>
+        <v>3.08</v>
       </c>
       <c r="V120" t="n">
-        <v>28.3</v>
+        <v>-300.3</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -9071,7 +9089,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>-13.5</v>
+        <v>24</v>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
@@ -9081,13 +9099,13 @@
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="n">
-        <v>4.88</v>
+        <v>1.58</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>94.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
@@ -9095,33 +9113,33 @@
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="R121" t="n">
-        <v>16.01</v>
+        <v>16.78</v>
       </c>
       <c r="S121" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T121" t="n">
-        <v>2.31</v>
+        <v>1.41</v>
       </c>
       <c r="U121" t="n">
-        <v>3.03</v>
+        <v>3.43</v>
       </c>
       <c r="V121" t="n">
-        <v>28.8</v>
+        <v>117.9</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>國票金</t>
+          <t>台中銀</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -9134,9 +9152,7 @@
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E122" t="n">
-        <v>-4.1</v>
-      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
         <v>0</v>
@@ -9145,13 +9161,13 @@
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="n">
-        <v>0.52</v>
+        <v>1.14</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>88.3</v>
+        <v>90.8</v>
       </c>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
@@ -9159,33 +9175,33 @@
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>15.1</v>
+        <v>19.6</v>
       </c>
       <c r="R122" t="n">
-        <v>23.89</v>
+        <v>12.84</v>
       </c>
       <c r="S122" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="T122" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="U122" t="n">
-        <v>3.92</v>
+        <v>5.39</v>
       </c>
       <c r="V122" t="n">
-        <v>147.9</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -9199,7 +9215,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>7.1</v>
+        <v>-24</v>
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
@@ -9209,13 +9225,13 @@
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="n">
-        <v>3.06</v>
+        <v>1.22</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>93.8</v>
+        <v>91.2</v>
       </c>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
@@ -9223,33 +9239,33 @@
         <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>70.5</v>
+        <v>30.4</v>
       </c>
       <c r="R123" t="n">
-        <v>17.28</v>
+        <v>17.44</v>
       </c>
       <c r="S123" t="n">
         <v>95</v>
       </c>
       <c r="T123" t="n">
-        <v>2.52</v>
+        <v>1.54</v>
       </c>
       <c r="U123" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="V123" t="n">
-        <v>76.09999999999999</v>
+        <v>-172.7</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -9263,7 +9279,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>12.2</v>
+        <v>7.1</v>
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
@@ -9273,13 +9289,13 @@
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="n">
-        <v>1.57</v>
+        <v>3.06</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
@@ -9287,33 +9303,33 @@
         <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>35.8</v>
+        <v>70.5</v>
       </c>
       <c r="R124" t="n">
-        <v>16.89</v>
+        <v>17.28</v>
       </c>
       <c r="S124" t="n">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="T124" t="n">
-        <v>2.03</v>
+        <v>2.52</v>
       </c>
       <c r="U124" t="n">
-        <v>3.91</v>
+        <v>3.55</v>
       </c>
       <c r="V124" t="n">
-        <v>24.8</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -9327,7 +9343,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1.9</v>
+        <v>12.2</v>
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
@@ -9337,13 +9353,13 @@
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>91.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
@@ -9351,177 +9367,161 @@
         <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>68.8</v>
+        <v>35.8</v>
       </c>
       <c r="R125" t="n">
-        <v>25.11</v>
+        <v>16.89</v>
       </c>
       <c r="S125" t="n">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="T125" t="n">
-        <v>2.53</v>
+        <v>2.03</v>
       </c>
       <c r="U125" t="n">
-        <v>3.24</v>
+        <v>3.91</v>
       </c>
       <c r="V125" t="n">
-        <v>227.3</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>今國光</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr"/>
+          <t>國票金</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>🏦</t>
+        </is>
+      </c>
       <c r="D126" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F126" t="n">
-        <v>-1.3</v>
-      </c>
+        <v>-4.1</v>
+      </c>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="H126" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="I126" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J126" t="n">
-        <v>7.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="n">
-        <v>1.73</v>
+        <v>0.52</v>
       </c>
       <c r="L126" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="N126" t="n">
-        <v>217</v>
-      </c>
-      <c r="O126" t="n">
-        <v>1.08</v>
-      </c>
+        <v>88.3</v>
+      </c>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
       <c r="P126" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>97.2</v>
+        <v>15.1</v>
       </c>
       <c r="R126" t="n">
-        <v>56.18</v>
+        <v>23.89</v>
       </c>
       <c r="S126" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="T126" t="n">
-        <v>4.97</v>
+        <v>1.17</v>
       </c>
       <c r="U126" t="n">
-        <v>0.51</v>
+        <v>3.92</v>
       </c>
       <c r="V126" t="n">
-        <v>70.7</v>
+        <v>147.9</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>揚明光</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>🏦</t>
+        </is>
+      </c>
       <c r="D127" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>-12.4</v>
-      </c>
-      <c r="F127" t="n">
-        <v>-4</v>
-      </c>
+        <v>-13.5</v>
+      </c>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="H127" t="n">
-        <v>18</v>
-      </c>
-      <c r="I127" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="J127" t="n">
-        <v>-0.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="n">
-        <v>-0.07000000000000001</v>
+        <v>4.88</v>
       </c>
       <c r="L127" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="N127" t="n">
-        <v>219</v>
-      </c>
-      <c r="O127" t="n">
-        <v>-41.26</v>
-      </c>
+        <v>94.3</v>
+      </c>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
       <c r="P127" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>53.1</v>
+        <v>113</v>
       </c>
       <c r="R127" t="n">
-        <v>132.75</v>
+        <v>16.01</v>
       </c>
       <c r="S127" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="T127" t="n">
-        <v>3.69</v>
+        <v>2.31</v>
       </c>
       <c r="U127" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="V127" t="n">
-        <v>16.1</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>新鉅科</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -9531,69 +9531,69 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>-1.6</v>
+        <v>0.3</v>
       </c>
       <c r="F128" t="n">
-        <v>-22.3</v>
+        <v>-1.3</v>
       </c>
       <c r="G128" t="n">
-        <v>-11.8</v>
+        <v>-0.7</v>
       </c>
       <c r="H128" t="n">
-        <v>8.6</v>
+        <v>23.9</v>
       </c>
       <c r="I128" t="n">
-        <v>-19</v>
+        <v>8.9</v>
       </c>
       <c r="J128" t="n">
-        <v>17.1</v>
+        <v>7.1</v>
       </c>
       <c r="K128" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="L128" t="n">
-        <v>14.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M128" t="n">
-        <v>31.3</v>
+        <v>33.3</v>
       </c>
       <c r="N128" t="n">
-        <v>293</v>
+        <v>217</v>
       </c>
       <c r="O128" t="n">
-        <v>-0.18</v>
+        <v>1.08</v>
       </c>
       <c r="P128" t="n">
-        <v>-10.3</v>
+        <v>-0.6</v>
       </c>
       <c r="Q128" t="n">
-        <v>33.6</v>
+        <v>97.2</v>
       </c>
       <c r="R128" t="n">
-        <v>16.02</v>
+        <v>56.18</v>
       </c>
       <c r="S128" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T128" t="n">
-        <v>2.3</v>
+        <v>4.97</v>
       </c>
       <c r="U128" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="V128" t="n">
-        <v>5.7</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>環宇-KY</t>
+          <t>揚明光</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -9603,69 +9603,69 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>15.3</v>
+        <v>-12.4</v>
       </c>
       <c r="F129" t="n">
-        <v>-36.2</v>
+        <v>-4</v>
       </c>
       <c r="G129" t="n">
-        <v>-12.6</v>
+        <v>-3.1</v>
       </c>
       <c r="H129" t="n">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="I129" t="n">
-        <v>22.4</v>
+        <v>-1.9</v>
       </c>
       <c r="J129" t="n">
-        <v>10.7</v>
+        <v>-0.3</v>
       </c>
       <c r="K129" t="n">
-        <v>2.53</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L129" t="n">
-        <v>6.9</v>
+        <v>-0.3</v>
       </c>
       <c r="M129" t="n">
-        <v>12.3</v>
+        <v>33.5</v>
       </c>
       <c r="N129" t="n">
-        <v>1077</v>
+        <v>219</v>
       </c>
       <c r="O129" t="n">
-        <v>2.3</v>
+        <v>-41.26</v>
       </c>
       <c r="P129" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q129" t="n">
-        <v>564</v>
+        <v>53.1</v>
       </c>
       <c r="R129" t="n">
-        <v>222.92</v>
+        <v>132.75</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="T129" t="n">
-        <v>16</v>
+        <v>3.69</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
       </c>
       <c r="V129" t="n">
-        <v>54.4</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>新鉅科</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -9675,69 +9675,69 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>120.6</v>
+        <v>-1.6</v>
       </c>
       <c r="F130" t="n">
-        <v>-122.9</v>
+        <v>-22.3</v>
       </c>
       <c r="G130" t="n">
-        <v>-13.5</v>
+        <v>-11.8</v>
       </c>
       <c r="H130" t="n">
-        <v>89</v>
+        <v>8.6</v>
       </c>
       <c r="I130" t="n">
-        <v>33.3</v>
+        <v>-19</v>
       </c>
       <c r="J130" t="n">
-        <v>33.3</v>
+        <v>17.1</v>
       </c>
       <c r="K130" t="n">
-        <v>16.26</v>
+        <v>2.1</v>
       </c>
       <c r="L130" t="n">
-        <v>17.2</v>
+        <v>14.4</v>
       </c>
       <c r="M130" t="n">
-        <v>14.1</v>
+        <v>31.3</v>
       </c>
       <c r="N130" t="n">
-        <v>653</v>
+        <v>293</v>
       </c>
       <c r="O130" t="n">
-        <v>1</v>
+        <v>-0.18</v>
       </c>
       <c r="P130" t="n">
-        <v>40.9</v>
+        <v>-10.3</v>
       </c>
       <c r="Q130" t="n">
-        <v>1060</v>
+        <v>33.6</v>
       </c>
       <c r="R130" t="n">
-        <v>65.19</v>
+        <v>16.02</v>
       </c>
       <c r="S130" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="T130" t="n">
-        <v>11.44</v>
+        <v>2.3</v>
       </c>
       <c r="U130" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="V130" t="n">
-        <v>108.5</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>博晟生醫</t>
+          <t>環宇-KY</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -9746,62 +9746,70 @@
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
+      <c r="E131" t="n">
+        <v>15.3</v>
+      </c>
       <c r="F131" t="n">
-        <v>-682.5</v>
+        <v>-36.2</v>
       </c>
       <c r="G131" t="n">
-        <v>-16.8</v>
+        <v>-12.6</v>
       </c>
       <c r="H131" t="n">
-        <v>71.2</v>
+        <v>51</v>
       </c>
       <c r="I131" t="n">
-        <v>-39.6</v>
+        <v>22.4</v>
       </c>
       <c r="J131" t="n">
-        <v>-33.9</v>
+        <v>10.7</v>
       </c>
       <c r="K131" t="n">
-        <v>-0.55</v>
+        <v>2.53</v>
       </c>
       <c r="L131" t="n">
-        <v>-6.9</v>
+        <v>6.9</v>
       </c>
       <c r="M131" t="n">
-        <v>4.1</v>
+        <v>12.3</v>
       </c>
       <c r="N131" t="n">
-        <v>3437</v>
+        <v>1077</v>
       </c>
       <c r="O131" t="n">
-        <v>0.58</v>
+        <v>2.3</v>
       </c>
       <c r="P131" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="Q131" t="inlineStr"/>
-      <c r="R131" t="inlineStr"/>
-      <c r="S131" t="inlineStr"/>
+        <v>5.1</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>564</v>
+      </c>
+      <c r="R131" t="n">
+        <v>222.92</v>
+      </c>
+      <c r="S131" t="n">
+        <v>5</v>
+      </c>
       <c r="T131" t="n">
-        <v>2.98</v>
+        <v>16</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
       </c>
       <c r="V131" t="n">
-        <v>-14.5</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>光環</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -9811,113 +9819,249 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>-15.3</v>
+        <v>120.6</v>
       </c>
       <c r="F132" t="n">
-        <v>-30.5</v>
+        <v>-122.9</v>
       </c>
       <c r="G132" t="n">
-        <v>-28.2</v>
+        <v>-13.5</v>
       </c>
       <c r="H132" t="n">
-        <v>7.3</v>
+        <v>89</v>
       </c>
       <c r="I132" t="n">
-        <v>-30.2</v>
+        <v>33.3</v>
       </c>
       <c r="J132" t="n">
-        <v>-31.4</v>
+        <v>33.3</v>
       </c>
       <c r="K132" t="n">
-        <v>-1.79</v>
+        <v>16.26</v>
       </c>
       <c r="L132" t="n">
-        <v>-27.9</v>
+        <v>17.2</v>
       </c>
       <c r="M132" t="n">
-        <v>42.4</v>
+        <v>14.1</v>
       </c>
       <c r="N132" t="n">
-        <v>209</v>
+        <v>653</v>
       </c>
       <c r="O132" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="P132" t="n">
-        <v>-0.7</v>
+        <v>40.9</v>
       </c>
       <c r="Q132" t="n">
-        <v>27.8</v>
+        <v>1060</v>
       </c>
       <c r="R132" t="n">
-        <v>308.33</v>
+        <v>65.19</v>
       </c>
       <c r="S132" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="T132" t="n">
-        <v>21.75</v>
+        <v>11.44</v>
       </c>
       <c r="U132" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="V132" t="n">
-        <v>13.3</v>
+        <v>108.5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>晶瑞光</t>
+          <t>博晟生醫</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
+      <c r="F133" t="n">
+        <v>-682.5</v>
+      </c>
+      <c r="G133" t="n">
+        <v>-16.8</v>
+      </c>
       <c r="H133" t="n">
-        <v>-54.1</v>
+        <v>71.2</v>
       </c>
       <c r="I133" t="n">
-        <v>-141.4</v>
+        <v>-39.6</v>
       </c>
       <c r="J133" t="n">
-        <v>-156.2</v>
+        <v>-33.9</v>
       </c>
       <c r="K133" t="n">
-        <v>-9.279999999999999</v>
+        <v>-0.55</v>
       </c>
       <c r="L133" t="n">
-        <v>-66.09999999999999</v>
+        <v>-6.9</v>
       </c>
       <c r="M133" t="n">
-        <v>12.5</v>
+        <v>4.1</v>
       </c>
       <c r="N133" t="n">
-        <v>455</v>
+        <v>3437</v>
       </c>
       <c r="O133" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="P133" t="n">
-        <v>-2.9</v>
+        <v>-0.3</v>
       </c>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr"/>
-      <c r="T133" t="inlineStr"/>
-      <c r="U133" t="inlineStr"/>
+      <c r="T133" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
       <c r="V133" t="n">
+        <v>-14.5</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>3234</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>光環</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>-15.3</v>
+      </c>
+      <c r="F134" t="n">
+        <v>-30.5</v>
+      </c>
+      <c r="G134" t="n">
+        <v>-28.2</v>
+      </c>
+      <c r="H134" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I134" t="n">
+        <v>-30.2</v>
+      </c>
+      <c r="J134" t="n">
+        <v>-31.4</v>
+      </c>
+      <c r="K134" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="L134" t="n">
+        <v>-27.9</v>
+      </c>
+      <c r="M134" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="N134" t="n">
+        <v>209</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P134" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="R134" t="n">
+        <v>308.33</v>
+      </c>
+      <c r="S134" t="n">
+        <v>3</v>
+      </c>
+      <c r="T134" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>6787</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>晶瑞光</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="n">
+        <v>-54.1</v>
+      </c>
+      <c r="I135" t="n">
+        <v>-141.4</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-156.2</v>
+      </c>
+      <c r="K135" t="n">
+        <v>-9.279999999999999</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-66.09999999999999</v>
+      </c>
+      <c r="M135" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="N135" t="n">
+        <v>455</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="P135" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="n">
         <v>58</v>
       </c>
     </row>
@@ -9932,7 +10076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X133"/>
+  <dimension ref="A1:X135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11428,229 +11572,229 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>茂達</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>37.1</v>
+        <v>36</v>
       </c>
       <c r="E20" t="n">
-        <v>35.7</v>
+        <v>36.4</v>
       </c>
       <c r="F20" t="n">
-        <v>73</v>
+        <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>18.3</v>
+        <v>1.7</v>
       </c>
       <c r="H20" t="n">
-        <v>16.7</v>
+        <v>2.1</v>
       </c>
       <c r="I20" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>16.3</v>
+        <v>1.5</v>
       </c>
       <c r="K20" t="n">
-        <v>14.7</v>
+        <v>2.2</v>
       </c>
       <c r="L20" t="n">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="M20" t="n">
-        <v>28.8</v>
+        <v>17.5</v>
       </c>
       <c r="N20" t="n">
-        <v>25.6</v>
+        <v>27.5</v>
       </c>
       <c r="O20" t="n">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>27.9</v>
+        <v>27.01</v>
       </c>
       <c r="Q20" t="n">
-        <v>19.06</v>
+        <v>25.03</v>
       </c>
       <c r="R20" t="n">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="S20" t="n">
-        <v>8.57</v>
+        <v>5.1</v>
       </c>
       <c r="T20" t="n">
-        <v>4.21</v>
+        <v>7.42</v>
       </c>
       <c r="U20" t="n">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="V20" t="n">
-        <v>2.79</v>
+        <v>3.46</v>
       </c>
       <c r="W20" t="n">
-        <v>4.66</v>
+        <v>3.33</v>
       </c>
       <c r="X20" t="n">
-        <v>7</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>敦陽科</t>
+          <t>茂達</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>23.9</v>
+        <v>37.1</v>
       </c>
       <c r="E21" t="n">
-        <v>24.8</v>
+        <v>35.7</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="G21" t="n">
-        <v>11.8</v>
+        <v>18.3</v>
       </c>
       <c r="H21" t="n">
-        <v>11.6</v>
+        <v>16.7</v>
       </c>
       <c r="I21" t="n">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="J21" t="n">
-        <v>10.2</v>
+        <v>16.3</v>
       </c>
       <c r="K21" t="n">
-        <v>10.3</v>
+        <v>14.7</v>
       </c>
       <c r="L21" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="M21" t="n">
-        <v>29.9</v>
+        <v>28.8</v>
       </c>
       <c r="N21" t="n">
-        <v>24.9</v>
+        <v>25.6</v>
       </c>
       <c r="O21" t="n">
+        <v>71</v>
+      </c>
+      <c r="P21" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="R21" t="n">
+        <v>91</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="U21" t="n">
         <v>100</v>
       </c>
-      <c r="P21" t="n">
-        <v>18.41</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>16.33</v>
-      </c>
-      <c r="R21" t="n">
-        <v>79</v>
-      </c>
-      <c r="S21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="U21" t="n">
-        <v>92</v>
-      </c>
       <c r="V21" t="n">
-        <v>5.05</v>
+        <v>2.79</v>
       </c>
       <c r="W21" t="n">
-        <v>5.79</v>
+        <v>4.66</v>
       </c>
       <c r="X21" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>敦陽科</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I22" t="n">
         <v>36</v>
       </c>
-      <c r="E22" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="F22" t="n">
-        <v>9</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>5</v>
-      </c>
       <c r="J22" t="n">
-        <v>1.5</v>
+        <v>10.2</v>
       </c>
       <c r="K22" t="n">
-        <v>2.2</v>
+        <v>10.3</v>
       </c>
       <c r="L22" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="M22" t="n">
-        <v>17.5</v>
+        <v>29.9</v>
       </c>
       <c r="N22" t="n">
-        <v>27.5</v>
+        <v>24.9</v>
       </c>
       <c r="O22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="P22" t="n">
-        <v>27.01</v>
+        <v>18.41</v>
       </c>
       <c r="Q22" t="n">
-        <v>25.03</v>
+        <v>16.33</v>
       </c>
       <c r="R22" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="S22" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="T22" t="n">
-        <v>7.42</v>
+        <v>3.78</v>
       </c>
       <c r="U22" t="n">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="V22" t="n">
-        <v>3.46</v>
+        <v>5.05</v>
       </c>
       <c r="W22" t="n">
-        <v>3.33</v>
+        <v>5.79</v>
       </c>
       <c r="X22" t="n">
-        <v>82</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -12036,153 +12180,153 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>大樹</t>
+          <t>長聖</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
-        <v>28.7</v>
+        <v>72.5</v>
       </c>
       <c r="E28" t="n">
-        <v>27.3</v>
+        <v>60.5</v>
       </c>
       <c r="F28" t="n">
         <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>3.3</v>
+        <v>44.8</v>
       </c>
       <c r="H28" t="n">
-        <v>4.5</v>
+        <v>29</v>
       </c>
       <c r="I28" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="J28" t="n">
-        <v>2.9</v>
+        <v>45.9</v>
       </c>
       <c r="K28" t="n">
-        <v>3.7</v>
+        <v>45.2</v>
       </c>
       <c r="L28" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="M28" t="n">
-        <v>15</v>
+        <v>16.7</v>
       </c>
       <c r="N28" t="n">
-        <v>21.4</v>
+        <v>20</v>
       </c>
       <c r="O28" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="P28" t="n">
-        <v>19</v>
+        <v>27.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>36.16</v>
+        <v>118.22</v>
       </c>
       <c r="R28" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="S28" t="n">
-        <v>3.12</v>
+        <v>4.87</v>
       </c>
       <c r="T28" t="n">
-        <v>7.45</v>
+        <v>9.82</v>
       </c>
       <c r="U28" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>5.06</v>
+        <v>2.81</v>
       </c>
       <c r="W28" t="n">
-        <v>2.66</v>
+        <v>2.37</v>
       </c>
       <c r="X28" t="n">
-        <v>98</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>長聖</t>
+          <t>大樹</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>72.5</v>
+        <v>28.7</v>
       </c>
       <c r="E29" t="n">
-        <v>60.5</v>
+        <v>27.3</v>
       </c>
       <c r="F29" t="n">
         <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>44.8</v>
+        <v>3.3</v>
       </c>
       <c r="H29" t="n">
-        <v>29</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="J29" t="n">
-        <v>45.9</v>
+        <v>2.9</v>
       </c>
       <c r="K29" t="n">
-        <v>45.2</v>
+        <v>3.7</v>
       </c>
       <c r="L29" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="M29" t="n">
-        <v>16.7</v>
+        <v>15</v>
       </c>
       <c r="N29" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="O29" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="P29" t="n">
-        <v>27.04</v>
+        <v>19</v>
       </c>
       <c r="Q29" t="n">
-        <v>118.22</v>
+        <v>36.16</v>
       </c>
       <c r="R29" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="S29" t="n">
-        <v>4.87</v>
+        <v>3.12</v>
       </c>
       <c r="T29" t="n">
-        <v>9.82</v>
+        <v>7.45</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="V29" t="n">
-        <v>2.81</v>
+        <v>5.06</v>
       </c>
       <c r="W29" t="n">
-        <v>2.37</v>
+        <v>2.66</v>
       </c>
       <c r="X29" t="n">
-        <v>46</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30">
@@ -13328,153 +13472,153 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>緯軟</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
-        <v>16.4</v>
+        <v>27</v>
       </c>
       <c r="E45" t="n">
-        <v>20.4</v>
+        <v>25.8</v>
       </c>
       <c r="F45" t="n">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="G45" t="n">
-        <v>6.3</v>
+        <v>20</v>
       </c>
       <c r="H45" t="n">
-        <v>6.8</v>
+        <v>18.4</v>
       </c>
       <c r="I45" t="n">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="J45" t="n">
-        <v>5.5</v>
+        <v>14.3</v>
       </c>
       <c r="K45" t="n">
-        <v>6.5</v>
+        <v>15.7</v>
       </c>
       <c r="L45" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="M45" t="n">
-        <v>15.9</v>
+        <v>17.9</v>
       </c>
       <c r="N45" t="n">
-        <v>17.7</v>
+        <v>18.8</v>
       </c>
       <c r="O45" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="P45" t="n">
-        <v>14.31</v>
+        <v>25.54</v>
       </c>
       <c r="Q45" t="n">
-        <v>14.46</v>
+        <v>13.67</v>
       </c>
       <c r="R45" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="S45" t="n">
-        <v>2.22</v>
+        <v>4.56</v>
       </c>
       <c r="T45" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U45" t="n">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="V45" t="n">
-        <v>3.88</v>
+        <v>3.23</v>
       </c>
       <c r="W45" t="n">
-        <v>4.34</v>
+        <v>6.16</v>
       </c>
       <c r="X45" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>緯軟</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="E46" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F46" t="n">
+        <v>9</v>
+      </c>
+      <c r="G46" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H46" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I46" t="n">
+        <v>32</v>
+      </c>
+      <c r="J46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L46" t="n">
         <v>27</v>
       </c>
-      <c r="E46" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="F46" t="n">
-        <v>73</v>
-      </c>
-      <c r="G46" t="n">
-        <v>20</v>
-      </c>
-      <c r="H46" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="I46" t="n">
-        <v>73</v>
-      </c>
-      <c r="J46" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K46" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="L46" t="n">
-        <v>41</v>
-      </c>
       <c r="M46" t="n">
-        <v>17.9</v>
+        <v>15.9</v>
       </c>
       <c r="N46" t="n">
-        <v>18.8</v>
+        <v>17.7</v>
       </c>
       <c r="O46" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="P46" t="n">
-        <v>25.54</v>
+        <v>14.31</v>
       </c>
       <c r="Q46" t="n">
-        <v>13.67</v>
+        <v>14.46</v>
       </c>
       <c r="R46" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="S46" t="n">
-        <v>4.56</v>
+        <v>2.22</v>
       </c>
       <c r="T46" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="U46" t="n">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="V46" t="n">
-        <v>3.23</v>
+        <v>3.88</v>
       </c>
       <c r="W46" t="n">
-        <v>6.16</v>
+        <v>4.34</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47">
@@ -13556,77 +13700,77 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
-        <v>35.5</v>
+        <v>25.9</v>
       </c>
       <c r="E48" t="n">
-        <v>30.7</v>
+        <v>25.6</v>
       </c>
       <c r="F48" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="G48" t="n">
-        <v>16.5</v>
+        <v>18.1</v>
       </c>
       <c r="H48" t="n">
-        <v>11.4</v>
+        <v>16.7</v>
       </c>
       <c r="I48" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J48" t="n">
-        <v>13.4</v>
+        <v>14.8</v>
       </c>
       <c r="K48" t="n">
-        <v>10.1</v>
+        <v>11.9</v>
       </c>
       <c r="L48" t="n">
         <v>100</v>
       </c>
       <c r="M48" t="n">
-        <v>22.3</v>
+        <v>18.6</v>
       </c>
       <c r="N48" t="n">
-        <v>17</v>
+        <v>16.7</v>
       </c>
       <c r="O48" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="P48" t="n">
-        <v>79.31</v>
+        <v>21.99</v>
       </c>
       <c r="Q48" t="n">
-        <v>32.09</v>
+        <v>22.15</v>
       </c>
       <c r="R48" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="S48" t="n">
-        <v>18.64</v>
+        <v>4.15</v>
       </c>
       <c r="T48" t="n">
-        <v>5.46</v>
+        <v>3.12</v>
       </c>
       <c r="U48" t="n">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="V48" t="n">
-        <v>0.54</v>
+        <v>3.31</v>
       </c>
       <c r="W48" t="n">
-        <v>2.11</v>
+        <v>3.48</v>
       </c>
       <c r="X48" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="49">
@@ -13708,77 +13852,77 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
-        <v>25.9</v>
+        <v>35.5</v>
       </c>
       <c r="E50" t="n">
-        <v>25.6</v>
+        <v>30.7</v>
       </c>
       <c r="F50" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="G50" t="n">
-        <v>18.1</v>
+        <v>16.5</v>
       </c>
       <c r="H50" t="n">
-        <v>16.7</v>
+        <v>11.4</v>
       </c>
       <c r="I50" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="J50" t="n">
-        <v>14.8</v>
+        <v>13.4</v>
       </c>
       <c r="K50" t="n">
-        <v>11.9</v>
+        <v>10.1</v>
       </c>
       <c r="L50" t="n">
         <v>100</v>
       </c>
       <c r="M50" t="n">
-        <v>18.6</v>
+        <v>22.3</v>
       </c>
       <c r="N50" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="O50" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="P50" t="n">
-        <v>21.99</v>
+        <v>79.31</v>
       </c>
       <c r="Q50" t="n">
-        <v>22.15</v>
+        <v>32.09</v>
       </c>
       <c r="R50" t="n">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="S50" t="n">
-        <v>4.15</v>
+        <v>18.64</v>
       </c>
       <c r="T50" t="n">
-        <v>3.12</v>
+        <v>5.46</v>
       </c>
       <c r="U50" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="V50" t="n">
-        <v>3.31</v>
+        <v>0.54</v>
       </c>
       <c r="W50" t="n">
-        <v>3.48</v>
+        <v>2.11</v>
       </c>
       <c r="X50" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -14320,77 +14464,77 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>閎康</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
-        <v>18.3</v>
+        <v>30.1</v>
       </c>
       <c r="E58" t="n">
-        <v>19.5</v>
+        <v>33.6</v>
       </c>
       <c r="F58" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="G58" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="H58" t="n">
-        <v>7.9</v>
+        <v>15.8</v>
       </c>
       <c r="I58" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>29.5</v>
+        <v>8.9</v>
       </c>
       <c r="K58" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="L58" t="n">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="M58" t="n">
-        <v>21.8</v>
+        <v>9.9</v>
       </c>
       <c r="N58" t="n">
-        <v>15.4</v>
+        <v>16.2</v>
       </c>
       <c r="O58" t="n">
+        <v>14</v>
+      </c>
+      <c r="P58" t="n">
+        <v>40.16</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>22.01</v>
+      </c>
+      <c r="R58" t="n">
+        <v>97</v>
+      </c>
+      <c r="S58" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="U58" t="n">
         <v>81</v>
       </c>
-      <c r="P58" t="n">
-        <v>100.69</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>37.76</v>
-      </c>
-      <c r="R58" t="n">
-        <v>94</v>
-      </c>
-      <c r="S58" t="n">
-        <v>21.95</v>
-      </c>
-      <c r="T58" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="U58" t="n">
-        <v>96</v>
-      </c>
       <c r="V58" t="n">
-        <v>0.4</v>
+        <v>1.48</v>
       </c>
       <c r="W58" t="n">
-        <v>3.12</v>
+        <v>3.46</v>
       </c>
       <c r="X58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -14472,77 +14616,77 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>閎康</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="n">
-        <v>30.1</v>
+        <v>18.3</v>
       </c>
       <c r="E60" t="n">
-        <v>33.6</v>
+        <v>19.5</v>
       </c>
       <c r="F60" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="G60" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="H60" t="n">
-        <v>15.8</v>
+        <v>7.9</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="J60" t="n">
-        <v>8.9</v>
+        <v>29.5</v>
       </c>
       <c r="K60" t="n">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
       <c r="L60" t="n">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="M60" t="n">
-        <v>9.9</v>
+        <v>21.8</v>
       </c>
       <c r="N60" t="n">
-        <v>16.2</v>
+        <v>15.4</v>
       </c>
       <c r="O60" t="n">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="P60" t="n">
-        <v>40.16</v>
+        <v>100.69</v>
       </c>
       <c r="Q60" t="n">
-        <v>22.01</v>
+        <v>37.76</v>
       </c>
       <c r="R60" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="S60" t="n">
-        <v>4.01</v>
+        <v>21.95</v>
       </c>
       <c r="T60" t="n">
-        <v>3.06</v>
+        <v>4.44</v>
       </c>
       <c r="U60" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="V60" t="n">
-        <v>1.48</v>
+        <v>0.4</v>
       </c>
       <c r="W60" t="n">
-        <v>3.46</v>
+        <v>3.12</v>
       </c>
       <c r="X60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -15308,153 +15452,153 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>台特化</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
-        <v>51.8</v>
+        <v>40.2</v>
       </c>
       <c r="E71" t="n">
-        <v>49.7</v>
+        <v>40</v>
       </c>
       <c r="F71" t="n">
         <v>55</v>
       </c>
       <c r="G71" t="n">
-        <v>41.2</v>
+        <v>21.6</v>
       </c>
       <c r="H71" t="n">
-        <v>38</v>
+        <v>22.2</v>
       </c>
       <c r="I71" t="n">
         <v>55</v>
       </c>
       <c r="J71" t="n">
-        <v>34.1</v>
+        <v>27.2</v>
       </c>
       <c r="K71" t="n">
-        <v>38</v>
+        <v>22.8</v>
       </c>
       <c r="L71" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="M71" t="n">
-        <v>20.7</v>
+        <v>14.7</v>
       </c>
       <c r="N71" t="n">
-        <v>17.2</v>
+        <v>14.1</v>
       </c>
       <c r="O71" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="P71" t="n">
-        <v>58.47</v>
+        <v>38.15</v>
       </c>
       <c r="Q71" t="n">
-        <v>61.81</v>
+        <v>25.2</v>
       </c>
       <c r="R71" t="n">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="S71" t="n">
-        <v>12.02</v>
+        <v>5.71</v>
       </c>
       <c r="T71" t="n">
-        <v>11.9</v>
+        <v>3.66</v>
       </c>
       <c r="U71" t="n">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="V71" t="n">
-        <v>1.06</v>
+        <v>1.57</v>
       </c>
       <c r="W71" t="n">
-        <v>0.77</v>
+        <v>2.38</v>
       </c>
       <c r="X71" t="n">
-        <v>92</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>台特化</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="n">
-        <v>40.2</v>
+        <v>51.8</v>
       </c>
       <c r="E72" t="n">
-        <v>40</v>
+        <v>49.7</v>
       </c>
       <c r="F72" t="n">
         <v>55</v>
       </c>
       <c r="G72" t="n">
-        <v>21.6</v>
+        <v>41.2</v>
       </c>
       <c r="H72" t="n">
-        <v>22.2</v>
+        <v>38</v>
       </c>
       <c r="I72" t="n">
         <v>55</v>
       </c>
       <c r="J72" t="n">
-        <v>27.2</v>
+        <v>34.1</v>
       </c>
       <c r="K72" t="n">
-        <v>22.8</v>
+        <v>38</v>
       </c>
       <c r="L72" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="M72" t="n">
-        <v>14.7</v>
+        <v>20.7</v>
       </c>
       <c r="N72" t="n">
-        <v>14.1</v>
+        <v>17.2</v>
       </c>
       <c r="O72" t="n">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="P72" t="n">
-        <v>38.15</v>
+        <v>58.47</v>
       </c>
       <c r="Q72" t="n">
-        <v>25.2</v>
+        <v>61.81</v>
       </c>
       <c r="R72" t="n">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="S72" t="n">
-        <v>5.71</v>
+        <v>12.02</v>
       </c>
       <c r="T72" t="n">
-        <v>3.66</v>
+        <v>11.9</v>
       </c>
       <c r="U72" t="n">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="V72" t="n">
-        <v>1.57</v>
+        <v>1.06</v>
       </c>
       <c r="W72" t="n">
-        <v>2.38</v>
+        <v>0.77</v>
       </c>
       <c r="X72" t="n">
-        <v>4</v>
+        <v>92</v>
       </c>
     </row>
     <row r="73">
@@ -16524,153 +16668,153 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>世禾</t>
+          <t>遠雄港</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="n">
-        <v>35.6</v>
+        <v>50.4</v>
       </c>
       <c r="E87" t="n">
-        <v>36.7</v>
+        <v>53.4</v>
       </c>
       <c r="F87" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="G87" t="n">
-        <v>17.5</v>
+        <v>39.3</v>
       </c>
       <c r="H87" t="n">
-        <v>17.6</v>
+        <v>37.6</v>
       </c>
       <c r="I87" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="J87" t="n">
-        <v>16.3</v>
+        <v>27</v>
       </c>
       <c r="K87" t="n">
-        <v>15.3</v>
+        <v>29.4</v>
       </c>
       <c r="L87" t="n">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="M87" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="N87" t="n">
         <v>10.5</v>
       </c>
       <c r="O87" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="P87" t="n">
-        <v>24.45</v>
+        <v>16.11</v>
       </c>
       <c r="Q87" t="n">
-        <v>15.15</v>
+        <v>18.42</v>
       </c>
       <c r="R87" t="n">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="S87" t="n">
-        <v>2.57</v>
+        <v>1.69</v>
       </c>
       <c r="T87" t="n">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="U87" t="n">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="V87" t="n">
-        <v>2.26</v>
+        <v>3.45</v>
       </c>
       <c r="W87" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="X87" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>遠雄港</t>
+          <t>世禾</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="n">
-        <v>50.4</v>
+        <v>35.6</v>
       </c>
       <c r="E88" t="n">
-        <v>53.4</v>
+        <v>36.7</v>
       </c>
       <c r="F88" t="n">
+        <v>5</v>
+      </c>
+      <c r="G88" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H88" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I88" t="n">
         <v>45</v>
       </c>
-      <c r="G88" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="H88" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="I88" t="n">
-        <v>64</v>
-      </c>
       <c r="J88" t="n">
-        <v>27</v>
+        <v>16.3</v>
       </c>
       <c r="K88" t="n">
-        <v>29.4</v>
+        <v>15.3</v>
       </c>
       <c r="L88" t="n">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="M88" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="N88" t="n">
         <v>10.5</v>
       </c>
       <c r="O88" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="P88" t="n">
-        <v>16.11</v>
+        <v>24.45</v>
       </c>
       <c r="Q88" t="n">
-        <v>18.42</v>
+        <v>15.15</v>
       </c>
       <c r="R88" t="n">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="S88" t="n">
-        <v>1.69</v>
+        <v>2.57</v>
       </c>
       <c r="T88" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="U88" t="n">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="V88" t="n">
-        <v>3.45</v>
+        <v>2.26</v>
       </c>
       <c r="W88" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="X88" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89">
@@ -17856,530 +18000,530 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>先進光</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
-        <v>17</v>
+        <v>29.3</v>
       </c>
       <c r="E105" t="n">
-        <v>21.9</v>
+        <v>32</v>
       </c>
       <c r="F105" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G105" t="n">
-        <v>-2</v>
+        <v>7.5</v>
       </c>
       <c r="H105" t="n">
-        <v>5.7</v>
+        <v>12.5</v>
       </c>
       <c r="I105" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J105" t="n">
-        <v>-6</v>
+        <v>6.1</v>
       </c>
       <c r="K105" t="n">
-        <v>-0.4</v>
+        <v>9.5</v>
       </c>
       <c r="L105" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="M105" t="n">
-        <v>-7.2</v>
+        <v>4</v>
       </c>
       <c r="N105" t="n">
-        <v>-4.6</v>
+        <v>7.8</v>
       </c>
       <c r="O105" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="P105" t="n">
-        <v>65.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="Q105" t="n">
-        <v>92.16</v>
+        <v>36.22</v>
       </c>
       <c r="R105" t="n">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="S105" t="n">
-        <v>8.01</v>
+        <v>3.16</v>
       </c>
       <c r="T105" t="n">
-        <v>4.98</v>
+        <v>2.9</v>
       </c>
       <c r="U105" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="V105" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W105" t="n">
-        <v>0.38</v>
+        <v>1.41</v>
       </c>
       <c r="X105" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>先進光</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
-        <v>6.9</v>
+        <v>17</v>
       </c>
       <c r="E106" t="n">
-        <v>4.9</v>
+        <v>21.9</v>
       </c>
       <c r="F106" t="n">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="G106" t="n">
-        <v>5.1</v>
+        <v>-2</v>
       </c>
       <c r="H106" t="n">
-        <v>3.2</v>
+        <v>5.7</v>
       </c>
       <c r="I106" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="J106" t="n">
-        <v>4.3</v>
+        <v>-6</v>
       </c>
       <c r="K106" t="n">
-        <v>3.5</v>
+        <v>-0.4</v>
       </c>
       <c r="L106" t="n">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="M106" t="n">
-        <v>7</v>
+        <v>-7.2</v>
       </c>
       <c r="N106" t="n">
-        <v>6.1</v>
+        <v>-4.6</v>
       </c>
       <c r="O106" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="P106" t="n">
-        <v>19.35</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="Q106" t="n">
-        <v>48.34</v>
+        <v>92.16</v>
       </c>
       <c r="R106" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="S106" t="n">
-        <v>1.36</v>
+        <v>8.01</v>
       </c>
       <c r="T106" t="n">
-        <v>2.23</v>
+        <v>4.98</v>
       </c>
       <c r="U106" t="n">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="V106" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>2.65</v>
+        <v>0.38</v>
       </c>
       <c r="X106" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>健喬</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="n">
-        <v>42.8</v>
+        <v>23.7</v>
       </c>
       <c r="E107" t="n">
-        <v>41.4</v>
+        <v>24.1</v>
       </c>
       <c r="F107" t="n">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="G107" t="n">
-        <v>11.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H107" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I107" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="J107" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="K107" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="L107" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="M107" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="N107" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="O107" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="P107" t="n">
-        <v>19.22</v>
+        <v>30.21</v>
       </c>
       <c r="Q107" t="n">
-        <v>19.73</v>
+        <v>20.24</v>
       </c>
       <c r="R107" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="S107" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="T107" t="n">
-        <v>1.93</v>
+        <v>1.23</v>
       </c>
       <c r="U107" t="n">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="V107" t="n">
-        <v>5.33</v>
+        <v>2.86</v>
       </c>
       <c r="W107" t="n">
-        <v>4.69</v>
+        <v>3.7</v>
       </c>
       <c r="X107" t="n">
-        <v>75</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>奈米醫材</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="n">
-        <v>58.6</v>
+        <v>6.9</v>
       </c>
       <c r="E108" t="n">
-        <v>75.8</v>
+        <v>4.9</v>
       </c>
       <c r="F108" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="G108" t="n">
-        <v>10.2</v>
+        <v>5.1</v>
       </c>
       <c r="H108" t="n">
-        <v>18.7</v>
+        <v>3.2</v>
       </c>
       <c r="I108" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="J108" t="n">
-        <v>-0.9</v>
+        <v>4.3</v>
       </c>
       <c r="K108" t="n">
-        <v>9.699999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="L108" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="M108" t="n">
-        <v>-0.5</v>
+        <v>7</v>
       </c>
       <c r="N108" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="O108" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="P108" t="n">
-        <v>85.76000000000001</v>
+        <v>19.35</v>
       </c>
       <c r="Q108" t="n">
-        <v>50.34</v>
+        <v>48.34</v>
       </c>
       <c r="R108" t="n">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="S108" t="n">
-        <v>1.84</v>
+        <v>1.36</v>
       </c>
       <c r="T108" t="n">
-        <v>3.53</v>
+        <v>2.23</v>
       </c>
       <c r="U108" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="V108" t="n">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="W108" t="n">
-        <v>0.8</v>
+        <v>2.65</v>
       </c>
       <c r="X108" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>健喬</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="n">
-        <v>48.8</v>
+        <v>42.8</v>
       </c>
       <c r="E109" t="n">
-        <v>32.3</v>
+        <v>41.4</v>
       </c>
       <c r="F109" t="n">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="G109" t="n">
-        <v>31.7</v>
+        <v>11.9</v>
       </c>
       <c r="H109" t="n">
-        <v>8.4</v>
+        <v>10.1</v>
       </c>
       <c r="I109" t="n">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="J109" t="n">
-        <v>26.7</v>
+        <v>9.4</v>
       </c>
       <c r="K109" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="L109" t="n">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="M109" t="n">
-        <v>16.6</v>
+        <v>5.9</v>
       </c>
       <c r="N109" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O109" t="n">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="P109" t="n">
-        <v>310.86</v>
+        <v>19.22</v>
       </c>
       <c r="Q109" t="n">
-        <v>186.74</v>
+        <v>19.73</v>
       </c>
       <c r="R109" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="S109" t="n">
-        <v>51.83</v>
+        <v>1.76</v>
       </c>
       <c r="T109" t="n">
-        <v>7.67</v>
+        <v>1.93</v>
       </c>
       <c r="U109" t="n">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="V109" t="n">
-        <v>0.17</v>
+        <v>5.33</v>
       </c>
       <c r="W109" t="n">
-        <v>1.57</v>
+        <v>4.69</v>
       </c>
       <c r="X109" t="n">
-        <v>21</v>
+        <v>75</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>奈米醫材</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
-        <v>18</v>
+        <v>58.6</v>
       </c>
       <c r="E110" t="n">
-        <v>19.1</v>
+        <v>75.8</v>
       </c>
       <c r="F110" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="G110" t="n">
-        <v>3</v>
+        <v>10.2</v>
       </c>
       <c r="H110" t="n">
-        <v>2.8</v>
+        <v>18.7</v>
       </c>
       <c r="I110" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="J110" t="n">
-        <v>0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="K110" t="n">
-        <v>5.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L110" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="M110" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="N110" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="O110" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="P110" t="n">
-        <v>2019.23</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="Q110" t="n">
-        <v>157.97</v>
+        <v>50.34</v>
       </c>
       <c r="R110" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="S110" t="n">
-        <v>9.34</v>
+        <v>1.84</v>
       </c>
       <c r="T110" t="n">
-        <v>2.47</v>
+        <v>3.53</v>
       </c>
       <c r="U110" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="V110" t="n">
-        <v>0.04</v>
+        <v>1.78</v>
       </c>
       <c r="W110" t="n">
-        <v>2.17</v>
+        <v>0.8</v>
       </c>
       <c r="X110" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>矽統</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>28.5</v>
+        <v>48.8</v>
       </c>
       <c r="E111" t="n">
-        <v>26.9</v>
+        <v>32.3</v>
       </c>
       <c r="F111" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="G111" t="n">
-        <v>0.5</v>
+        <v>31.7</v>
       </c>
       <c r="H111" t="n">
-        <v>-163.4</v>
+        <v>8.4</v>
       </c>
       <c r="I111" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="J111" t="n">
-        <v>25.3</v>
+        <v>26.7</v>
       </c>
       <c r="K111" t="n">
-        <v>110.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L111" t="n">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="M111" t="n">
-        <v>4.2</v>
+        <v>16.6</v>
       </c>
       <c r="N111" t="n">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="O111" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P111" t="n">
-        <v>40.65</v>
+        <v>310.86</v>
       </c>
       <c r="Q111" t="n">
-        <v>54.61</v>
+        <v>186.74</v>
       </c>
       <c r="R111" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="S111" t="n">
-        <v>1.75</v>
+        <v>51.83</v>
       </c>
       <c r="T111" t="n">
-        <v>1.26</v>
+        <v>7.67</v>
       </c>
       <c r="U111" t="n">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="V111" t="n">
-        <v>0.87</v>
+        <v>0.17</v>
       </c>
       <c r="W111" t="n">
-        <v>5.46</v>
+        <v>1.57</v>
       </c>
       <c r="X111" t="n">
         <v>21</v>
@@ -18388,400 +18532,392 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>上詮</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
-        <v>15.7</v>
+        <v>18</v>
       </c>
       <c r="E112" t="n">
-        <v>17.4</v>
+        <v>19.1</v>
       </c>
       <c r="F112" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="G112" t="n">
-        <v>-8</v>
+        <v>3</v>
       </c>
       <c r="H112" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="I112" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="J112" t="n">
-        <v>-4.9</v>
+        <v>0.5</v>
       </c>
       <c r="K112" t="n">
-        <v>2.7</v>
+        <v>5.7</v>
       </c>
       <c r="L112" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="M112" t="n">
-        <v>-1.6</v>
+        <v>0.5</v>
       </c>
       <c r="N112" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="O112" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="P112" t="n">
-        <v>5637.5</v>
+        <v>2019.23</v>
       </c>
       <c r="Q112" t="n">
-        <v>1022.54</v>
+        <v>157.97</v>
       </c>
       <c r="R112" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="S112" t="n">
-        <v>14.11</v>
+        <v>9.34</v>
       </c>
       <c r="T112" t="n">
-        <v>5.67</v>
+        <v>2.47</v>
       </c>
       <c r="U112" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="V112" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="W112" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="X112" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>精確</t>
+          <t>矽統</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>28.5</v>
       </c>
       <c r="E113" t="n">
-        <v>13</v>
+        <v>26.9</v>
       </c>
       <c r="F113" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G113" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>-163.4</v>
       </c>
       <c r="I113" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="J113" t="n">
-        <v>2.1</v>
+        <v>25.3</v>
       </c>
       <c r="K113" t="n">
-        <v>1</v>
+        <v>110.7</v>
       </c>
       <c r="L113" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="M113" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="N113" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O113" t="n">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="P113" t="n">
-        <v>69.34</v>
+        <v>40.65</v>
       </c>
       <c r="Q113" t="n">
-        <v>74.56999999999999</v>
+        <v>54.61</v>
       </c>
       <c r="R113" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="S113" t="n">
-        <v>3.17</v>
+        <v>1.75</v>
       </c>
       <c r="T113" t="n">
-        <v>3.24</v>
+        <v>1.26</v>
       </c>
       <c r="U113" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="V113" t="n">
-        <v>1.18</v>
+        <v>0.87</v>
       </c>
       <c r="W113" t="n">
-        <v>0.21</v>
+        <v>5.46</v>
       </c>
       <c r="X113" t="n">
-        <v>96</v>
+        <v>21</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>訊連</t>
+          <t>上詮</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
-        <v>84</v>
+        <v>15.7</v>
       </c>
       <c r="E114" t="n">
-        <v>85.7</v>
+        <v>17.4</v>
       </c>
       <c r="F114" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="G114" t="n">
-        <v>15.3</v>
+        <v>-8</v>
       </c>
       <c r="H114" t="n">
-        <v>11.4</v>
+        <v>1.6</v>
       </c>
       <c r="I114" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="J114" t="n">
-        <v>11.7</v>
+        <v>-4.9</v>
       </c>
       <c r="K114" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="L114" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="M114" t="n">
-        <v>6.1</v>
+        <v>-1.6</v>
       </c>
       <c r="N114" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="O114" t="n">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="P114" t="n">
-        <v>18.75</v>
+        <v>5637.5</v>
       </c>
       <c r="Q114" t="n">
-        <v>35.61</v>
+        <v>1022.54</v>
       </c>
       <c r="R114" t="n">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="S114" t="n">
-        <v>1.14</v>
+        <v>14.11</v>
       </c>
       <c r="T114" t="n">
-        <v>1.9</v>
+        <v>5.67</v>
       </c>
       <c r="U114" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="V114" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>2.99</v>
+        <v>2.36</v>
       </c>
       <c r="X114" t="n">
-        <v>96</v>
+        <v>21</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>🏦</t>
-        </is>
-      </c>
+          <t>精確</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F115" t="n">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O115" t="n">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="P115" t="n">
-        <v>16.78</v>
+        <v>69.34</v>
       </c>
       <c r="Q115" t="n">
-        <v>14.04</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="R115" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="S115" t="n">
-        <v>1.41</v>
+        <v>3.17</v>
       </c>
       <c r="T115" t="n">
-        <v>1.05</v>
+        <v>3.24</v>
       </c>
       <c r="U115" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="V115" t="n">
-        <v>3.43</v>
+        <v>1.18</v>
       </c>
       <c r="W115" t="n">
-        <v>5.66</v>
+        <v>0.21</v>
       </c>
       <c r="X115" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>永豐金</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>🏦</t>
-        </is>
-      </c>
+          <t>訊連</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="F116" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>15.3</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="I116" t="n">
         <v>100</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="L116" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O116" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="P116" t="n">
-        <v>20.2</v>
+        <v>18.75</v>
       </c>
       <c r="Q116" t="n">
-        <v>12.83</v>
+        <v>35.61</v>
       </c>
       <c r="R116" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="S116" t="n">
-        <v>2.17</v>
+        <v>1.14</v>
       </c>
       <c r="T116" t="n">
-        <v>1.26</v>
+        <v>1.9</v>
       </c>
       <c r="U116" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="V116" t="n">
-        <v>3.27</v>
+        <v>5.22</v>
       </c>
       <c r="W116" t="n">
-        <v>4.93</v>
+        <v>2.99</v>
       </c>
       <c r="X116" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -18826,42 +18962,42 @@
         <v>100</v>
       </c>
       <c r="P117" t="n">
-        <v>17.44</v>
+        <v>19.79</v>
       </c>
       <c r="Q117" t="n">
-        <v>10.92</v>
+        <v>16.99</v>
       </c>
       <c r="R117" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S117" t="n">
-        <v>1.54</v>
+        <v>2.15</v>
       </c>
       <c r="T117" t="n">
-        <v>0.99</v>
+        <v>1.55</v>
       </c>
       <c r="U117" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="V117" t="n">
-        <v>3.25</v>
+        <v>3.86</v>
       </c>
       <c r="W117" t="n">
-        <v>4.53</v>
+        <v>4.35</v>
       </c>
       <c r="X117" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -18906,42 +19042,42 @@
         <v>100</v>
       </c>
       <c r="P118" t="n">
-        <v>16.55</v>
+        <v>20.2</v>
       </c>
       <c r="Q118" t="n">
-        <v>16.68</v>
+        <v>12.83</v>
       </c>
       <c r="R118" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="S118" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="T118" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="U118" t="n">
         <v>100</v>
       </c>
       <c r="V118" t="n">
-        <v>3.08</v>
+        <v>3.27</v>
       </c>
       <c r="W118" t="n">
-        <v>4.12</v>
+        <v>4.93</v>
       </c>
       <c r="X118" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -18986,42 +19122,42 @@
         <v>100</v>
       </c>
       <c r="P119" t="n">
-        <v>19.79</v>
+        <v>25.11</v>
       </c>
       <c r="Q119" t="n">
-        <v>16.99</v>
+        <v>12.49</v>
       </c>
       <c r="R119" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="S119" t="n">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="T119" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="U119" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="V119" t="n">
-        <v>3.86</v>
+        <v>3.24</v>
       </c>
       <c r="W119" t="n">
-        <v>4.35</v>
+        <v>5.23</v>
       </c>
       <c r="X119" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>台中銀</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -19029,55 +19165,79 @@
           <t>🏦</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>100</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>100</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>100</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>100</v>
+      </c>
       <c r="P120" t="n">
-        <v>12.84</v>
+        <v>16.55</v>
       </c>
       <c r="Q120" t="n">
-        <v>12.67</v>
+        <v>16.68</v>
       </c>
       <c r="R120" t="n">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="S120" t="n">
-        <v>1.26</v>
+        <v>2.11</v>
       </c>
       <c r="T120" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="U120" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="V120" t="n">
-        <v>5.39</v>
+        <v>3.08</v>
       </c>
       <c r="W120" t="n">
-        <v>5.67</v>
+        <v>4.12</v>
       </c>
       <c r="X120" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -19122,42 +19282,42 @@
         <v>100</v>
       </c>
       <c r="P121" t="n">
-        <v>16.01</v>
+        <v>16.78</v>
       </c>
       <c r="Q121" t="n">
-        <v>15.79</v>
+        <v>14.04</v>
       </c>
       <c r="R121" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S121" t="n">
-        <v>2.31</v>
+        <v>1.41</v>
       </c>
       <c r="T121" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="U121" t="n">
         <v>100</v>
       </c>
       <c r="V121" t="n">
-        <v>3.03</v>
+        <v>3.43</v>
       </c>
       <c r="W121" t="n">
-        <v>4.53</v>
+        <v>5.66</v>
       </c>
       <c r="X121" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>國票金</t>
+          <t>台中銀</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -19165,79 +19325,55 @@
           <t>🏦</t>
         </is>
       </c>
-      <c r="D122" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" t="n">
-        <v>100</v>
-      </c>
-      <c r="G122" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" t="n">
-        <v>100</v>
-      </c>
-      <c r="J122" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" t="n">
-        <v>100</v>
-      </c>
-      <c r="M122" t="n">
-        <v>0</v>
-      </c>
-      <c r="N122" t="n">
-        <v>0</v>
-      </c>
-      <c r="O122" t="n">
-        <v>100</v>
-      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
       <c r="P122" t="n">
-        <v>23.89</v>
+        <v>12.84</v>
       </c>
       <c r="Q122" t="n">
-        <v>21.57</v>
+        <v>12.67</v>
       </c>
       <c r="R122" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="S122" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="T122" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="U122" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="V122" t="n">
-        <v>3.92</v>
+        <v>5.39</v>
       </c>
       <c r="W122" t="n">
-        <v>5.65</v>
+        <v>5.67</v>
       </c>
       <c r="X122" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -19282,42 +19418,42 @@
         <v>100</v>
       </c>
       <c r="P123" t="n">
-        <v>17.28</v>
+        <v>17.44</v>
       </c>
       <c r="Q123" t="n">
-        <v>11.6</v>
+        <v>10.92</v>
       </c>
       <c r="R123" t="n">
         <v>95</v>
       </c>
       <c r="S123" t="n">
-        <v>2.52</v>
+        <v>1.54</v>
       </c>
       <c r="T123" t="n">
-        <v>1.39</v>
+        <v>0.99</v>
       </c>
       <c r="U123" t="n">
         <v>100</v>
       </c>
       <c r="V123" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="W123" t="n">
-        <v>4.76</v>
+        <v>4.53</v>
       </c>
       <c r="X123" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -19362,42 +19498,42 @@
         <v>100</v>
       </c>
       <c r="P124" t="n">
-        <v>16.89</v>
+        <v>17.28</v>
       </c>
       <c r="Q124" t="n">
-        <v>18.88</v>
+        <v>11.6</v>
       </c>
       <c r="R124" t="n">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="S124" t="n">
-        <v>2.03</v>
+        <v>2.52</v>
       </c>
       <c r="T124" t="n">
-        <v>1.86</v>
+        <v>1.39</v>
       </c>
       <c r="U124" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="V124" t="n">
-        <v>3.91</v>
+        <v>3.55</v>
       </c>
       <c r="W124" t="n">
-        <v>4.5</v>
+        <v>4.76</v>
       </c>
       <c r="X124" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -19442,616 +19578,776 @@
         <v>100</v>
       </c>
       <c r="P125" t="n">
-        <v>25.11</v>
+        <v>16.89</v>
       </c>
       <c r="Q125" t="n">
-        <v>12.49</v>
+        <v>18.88</v>
       </c>
       <c r="R125" t="n">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="S125" t="n">
-        <v>2.53</v>
+        <v>2.03</v>
       </c>
       <c r="T125" t="n">
-        <v>1.22</v>
+        <v>1.86</v>
       </c>
       <c r="U125" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="V125" t="n">
-        <v>3.24</v>
+        <v>3.91</v>
       </c>
       <c r="W125" t="n">
-        <v>5.23</v>
+        <v>4.5</v>
       </c>
       <c r="X125" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>今國光</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr"/>
+          <t>國票金</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>🏦</t>
+        </is>
+      </c>
       <c r="D126" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F126" t="n">
         <v>100</v>
       </c>
       <c r="G126" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>-3.7</v>
+        <v>0</v>
       </c>
       <c r="I126" t="n">
         <v>100</v>
       </c>
       <c r="J126" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>-1.9</v>
+        <v>0</v>
       </c>
       <c r="L126" t="n">
         <v>100</v>
       </c>
       <c r="M126" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>-1.7</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>100</v>
       </c>
       <c r="P126" t="n">
-        <v>56.18</v>
+        <v>23.89</v>
       </c>
       <c r="Q126" t="n">
-        <v>159.72</v>
+        <v>21.57</v>
       </c>
       <c r="R126" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="S126" t="n">
-        <v>4.97</v>
+        <v>1.17</v>
       </c>
       <c r="T126" t="n">
-        <v>1.83</v>
+        <v>1.14</v>
       </c>
       <c r="U126" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="V126" t="n">
-        <v>0.51</v>
+        <v>3.92</v>
       </c>
       <c r="W126" t="n">
-        <v>1.06</v>
+        <v>5.65</v>
       </c>
       <c r="X126" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>揚明光</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>🏦</t>
+        </is>
+      </c>
       <c r="D127" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>15.1</v>
+        <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="G127" t="n">
-        <v>-1.9</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>-4.6</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="J127" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>-3.7</v>
+        <v>0</v>
       </c>
       <c r="L127" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="M127" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>-3.1</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="P127" t="n">
-        <v>132.75</v>
+        <v>16.01</v>
       </c>
       <c r="Q127" t="n">
-        <v>122.39</v>
+        <v>15.79</v>
       </c>
       <c r="R127" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="S127" t="n">
-        <v>3.69</v>
+        <v>2.31</v>
       </c>
       <c r="T127" t="n">
-        <v>2.6</v>
+        <v>1.11</v>
       </c>
       <c r="U127" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="V127" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="W127" t="n">
-        <v>0.06</v>
+        <v>4.53</v>
       </c>
       <c r="X127" t="n">
-        <v>93</v>
+        <v>22</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>新鉅科</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="n">
-        <v>8.9</v>
+        <v>24.3</v>
       </c>
       <c r="E128" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="F128" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="G128" t="n">
-        <v>-18.8</v>
+        <v>9.5</v>
       </c>
       <c r="H128" t="n">
-        <v>-30.8</v>
+        <v>-3.7</v>
       </c>
       <c r="I128" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="J128" t="n">
-        <v>18</v>
+        <v>7.5</v>
       </c>
       <c r="K128" t="n">
-        <v>-19.4</v>
+        <v>-1.9</v>
       </c>
       <c r="L128" t="n">
         <v>100</v>
       </c>
       <c r="M128" t="n">
-        <v>14.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N128" t="n">
-        <v>-10.6</v>
+        <v>-1.7</v>
       </c>
       <c r="O128" t="n">
         <v>100</v>
       </c>
       <c r="P128" t="n">
-        <v>16.02</v>
+        <v>56.18</v>
       </c>
       <c r="Q128" t="n">
-        <v>23.86</v>
+        <v>159.72</v>
       </c>
       <c r="R128" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="S128" t="n">
-        <v>2.3</v>
+        <v>4.97</v>
       </c>
       <c r="T128" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="U128" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="V128" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="W128" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X128" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>環宇-KY</t>
+          <t>揚明光</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
-        <v>51.5</v>
+        <v>18</v>
       </c>
       <c r="E129" t="n">
-        <v>31.4</v>
+        <v>15.1</v>
       </c>
       <c r="F129" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="G129" t="n">
-        <v>22.6</v>
+        <v>-1.9</v>
       </c>
       <c r="H129" t="n">
-        <v>0.6</v>
+        <v>-4.6</v>
       </c>
       <c r="I129" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="J129" t="n">
-        <v>12</v>
+        <v>-0.3</v>
       </c>
       <c r="K129" t="n">
-        <v>-33.3</v>
+        <v>-3.7</v>
       </c>
       <c r="L129" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="M129" t="n">
-        <v>6.9</v>
+        <v>-0.3</v>
       </c>
       <c r="N129" t="n">
-        <v>-12.4</v>
+        <v>-3.1</v>
       </c>
       <c r="O129" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="P129" t="n">
-        <v>222.92</v>
+        <v>132.75</v>
       </c>
       <c r="Q129" t="n">
-        <v>1255.25</v>
+        <v>122.39</v>
       </c>
       <c r="R129" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="S129" t="n">
-        <v>16</v>
+        <v>3.69</v>
       </c>
       <c r="T129" t="n">
-        <v>2.93</v>
+        <v>2.6</v>
       </c>
       <c r="U129" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="V129" t="n">
         <v>0</v>
       </c>
       <c r="W129" t="n">
-        <v>0.21</v>
+        <v>0.06</v>
       </c>
       <c r="X129" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>新鉅科</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>88.90000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="E130" t="n">
-        <v>70.2</v>
+        <v>5.1</v>
       </c>
       <c r="F130" t="n">
+        <v>82</v>
+      </c>
+      <c r="G130" t="n">
+        <v>-18.8</v>
+      </c>
+      <c r="H130" t="n">
+        <v>-30.8</v>
+      </c>
+      <c r="I130" t="n">
         <v>86</v>
       </c>
-      <c r="G130" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="H130" t="n">
-        <v>-118.6</v>
-      </c>
-      <c r="I130" t="n">
+      <c r="J130" t="n">
+        <v>18</v>
+      </c>
+      <c r="K130" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="L130" t="n">
         <v>100</v>
       </c>
-      <c r="J130" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="K130" t="n">
-        <v>-115.3</v>
-      </c>
-      <c r="L130" t="n">
-        <v>91</v>
-      </c>
       <c r="M130" t="n">
-        <v>17.2</v>
+        <v>14.4</v>
       </c>
       <c r="N130" t="n">
-        <v>-25.6</v>
+        <v>-10.6</v>
       </c>
       <c r="O130" t="n">
         <v>100</v>
       </c>
       <c r="P130" t="n">
-        <v>65.19</v>
+        <v>16.02</v>
       </c>
       <c r="Q130" t="n">
-        <v>110.65</v>
+        <v>23.86</v>
       </c>
       <c r="R130" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="S130" t="n">
-        <v>11.44</v>
+        <v>2.3</v>
       </c>
       <c r="T130" t="n">
-        <v>11.69</v>
+        <v>1.94</v>
       </c>
       <c r="U130" t="n">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="V130" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="W130" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="X130" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>博晟生醫</t>
+          <t>環宇-KY</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="n">
-        <v>74.3</v>
+        <v>51.5</v>
       </c>
       <c r="E131" t="n">
-        <v>78.8</v>
+        <v>31.4</v>
       </c>
       <c r="F131" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="G131" t="n">
-        <v>-40.7</v>
+        <v>22.6</v>
       </c>
       <c r="H131" t="n">
-        <v>-342.9</v>
+        <v>0.6</v>
       </c>
       <c r="I131" t="n">
         <v>100</v>
       </c>
       <c r="J131" t="n">
-        <v>-34.8</v>
+        <v>12</v>
       </c>
       <c r="K131" t="n">
-        <v>-299.4</v>
+        <v>-33.3</v>
       </c>
       <c r="L131" t="n">
         <v>100</v>
       </c>
       <c r="M131" t="n">
-        <v>-6.9</v>
+        <v>6.9</v>
       </c>
       <c r="N131" t="n">
-        <v>-16.2</v>
+        <v>-12.4</v>
       </c>
       <c r="O131" t="n">
         <v>100</v>
       </c>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
-      <c r="R131" t="inlineStr"/>
+      <c r="P131" t="n">
+        <v>222.92</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>1255.25</v>
+      </c>
+      <c r="R131" t="n">
+        <v>5</v>
+      </c>
       <c r="S131" t="n">
-        <v>2.98</v>
+        <v>16</v>
       </c>
       <c r="T131" t="n">
-        <v>4.25</v>
+        <v>2.93</v>
       </c>
       <c r="U131" t="n">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="V131" t="n">
         <v>0</v>
       </c>
       <c r="W131" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="X131" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>光環</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="n">
-        <v>7.6</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="E132" t="n">
-        <v>14.6</v>
+        <v>70.2</v>
       </c>
       <c r="F132" t="n">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="G132" t="n">
-        <v>-30.3</v>
+        <v>33.8</v>
       </c>
       <c r="H132" t="n">
-        <v>-22.6</v>
+        <v>-118.6</v>
       </c>
       <c r="I132" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="J132" t="n">
-        <v>-31.3</v>
+        <v>33.9</v>
       </c>
       <c r="K132" t="n">
-        <v>-26.1</v>
+        <v>-115.3</v>
       </c>
       <c r="L132" t="n">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="M132" t="n">
-        <v>-27.9</v>
+        <v>17.2</v>
       </c>
       <c r="N132" t="n">
-        <v>-23</v>
+        <v>-25.6</v>
       </c>
       <c r="O132" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="P132" t="n">
-        <v>308.33</v>
+        <v>65.19</v>
       </c>
       <c r="Q132" t="n">
-        <v>407.98</v>
+        <v>110.65</v>
       </c>
       <c r="R132" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="S132" t="n">
-        <v>21.75</v>
+        <v>11.44</v>
       </c>
       <c r="T132" t="n">
-        <v>4.12</v>
+        <v>11.69</v>
       </c>
       <c r="U132" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="V132" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W132" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="X132" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>晶瑞光</t>
+          <t>博晟生醫</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="n">
-        <v>-52.9</v>
+        <v>74.3</v>
       </c>
       <c r="E133" t="n">
-        <v>-146.5</v>
+        <v>78.8</v>
       </c>
       <c r="F133" t="n">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="G133" t="n">
-        <v>-137</v>
+        <v>-40.7</v>
       </c>
       <c r="H133" t="n">
-        <v>-285.2</v>
+        <v>-342.9</v>
       </c>
       <c r="I133" t="n">
         <v>100</v>
       </c>
       <c r="J133" t="n">
-        <v>-152.1</v>
+        <v>-34.8</v>
       </c>
       <c r="K133" t="n">
-        <v>-280</v>
+        <v>-299.4</v>
       </c>
       <c r="L133" t="n">
         <v>100</v>
       </c>
       <c r="M133" t="n">
-        <v>-66.09999999999999</v>
+        <v>-6.9</v>
       </c>
       <c r="N133" t="n">
-        <v>-48.1</v>
+        <v>-16.2</v>
       </c>
       <c r="O133" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
-      <c r="S133" t="inlineStr"/>
-      <c r="T133" t="inlineStr"/>
-      <c r="U133" t="inlineStr"/>
-      <c r="V133" t="inlineStr"/>
-      <c r="W133" t="inlineStr"/>
-      <c r="X133" t="inlineStr"/>
+      <c r="S133" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T133" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="U133" t="n">
+        <v>25</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>3234</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>光環</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E134" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F134" t="n">
+        <v>27</v>
+      </c>
+      <c r="G134" t="n">
+        <v>-30.3</v>
+      </c>
+      <c r="H134" t="n">
+        <v>-22.6</v>
+      </c>
+      <c r="I134" t="n">
+        <v>32</v>
+      </c>
+      <c r="J134" t="n">
+        <v>-31.3</v>
+      </c>
+      <c r="K134" t="n">
+        <v>-26.1</v>
+      </c>
+      <c r="L134" t="n">
+        <v>32</v>
+      </c>
+      <c r="M134" t="n">
+        <v>-27.9</v>
+      </c>
+      <c r="N134" t="n">
+        <v>-23</v>
+      </c>
+      <c r="O134" t="n">
+        <v>33</v>
+      </c>
+      <c r="P134" t="n">
+        <v>308.33</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>407.98</v>
+      </c>
+      <c r="R134" t="n">
+        <v>3</v>
+      </c>
+      <c r="S134" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="T134" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="U134" t="n">
+        <v>100</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0</v>
+      </c>
+      <c r="X134" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>6787</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>晶瑞光</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="n">
+        <v>-52.9</v>
+      </c>
+      <c r="E135" t="n">
+        <v>-146.5</v>
+      </c>
+      <c r="F135" t="n">
+        <v>100</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-137</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-285.2</v>
+      </c>
+      <c r="I135" t="n">
+        <v>100</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-152.1</v>
+      </c>
+      <c r="K135" t="n">
+        <v>-280</v>
+      </c>
+      <c r="L135" t="n">
+        <v>100</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-66.09999999999999</v>
+      </c>
+      <c r="N135" t="n">
+        <v>-48.1</v>
+      </c>
+      <c r="O135" t="n">
+        <v>11</v>
+      </c>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr"/>
+      <c r="W135" t="inlineStr"/>
+      <c r="X135" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20064,7 +20360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22950,6 +23246,50 @@
       </c>
       <c r="F132" t="n">
         <v>6261.7</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>1504 東元</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>525.6</v>
+      </c>
+      <c r="C133" t="n">
+        <v>583.2</v>
+      </c>
+      <c r="D133" t="n">
+        <v>593.9</v>
+      </c>
+      <c r="E133" t="n">
+        <v>552.4</v>
+      </c>
+      <c r="F133" t="n">
+        <v>590.9</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>2049 上銀</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>272.7</v>
+      </c>
+      <c r="C134" t="n">
+        <v>293.2</v>
+      </c>
+      <c r="D134" t="n">
+        <v>246.3</v>
+      </c>
+      <c r="E134" t="n">
+        <v>244</v>
+      </c>
+      <c r="F134" t="n">
+        <v>242.7</v>
       </c>
     </row>
   </sheetData>
@@ -22963,7 +23303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25851,6 +26191,50 @@
         <v>1.04</v>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>1504 東元</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="D133" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E133" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>2049 上銀</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="C134" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="D134" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="E134" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="F134" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
